--- a/data/monthly/【2026年2月】月次数値.xlsx
+++ b/data/monthly/【2026年2月】月次数値.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="247">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -400,13 +400,488 @@
   </si>
   <si>
     <t>Beauty Salon Arona</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Dining Bar Lien】...</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌸【女性クリニック ラポール】🌸
+すべての世代の女性に、安心と寄り添いを。...</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍Wild Crepes - ワイルドクレープス
+安い！旨い！多い！🎉...</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍸【bar moon walk 三条木屋町店】🌙...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶【駕町 とくさ】熊本・花畑町駅 徒歩5分...</t>
+  </si>
+  <si>
+    <t>炭焼　猿一</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>島田屋　東苗穂店</t>
+  </si>
+  <si>
+    <t>居ZAKKU　CHENOWA</t>
+  </si>
+  <si>
+    <t>三千段の民宿　幸登里</t>
+  </si>
+  <si>
+    <t>てんぐ屋</t>
+  </si>
+  <si>
+    <t>炭火焼肉友丸</t>
+  </si>
+  <si>
+    <t>旬彩屋　笑味</t>
+  </si>
+  <si>
+    <t>有限会社　大嶋_うまか喰い処 祇園 大しま</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【海鮮と肉料理 ほっかい酒房】🍣🍢✨
+すすきの駅から徒歩3分🚶‍♂️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【せがわ歯科クリニック】です🦷✨...</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【ORINAS】です🍽️✨...</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【CasualClub青】です🎤✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Mix Bar Blo】です🍸✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【はんすう】です🍦✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 新潟県長岡市に佇むカフェ『樹林館』🌳☕️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 「新潟県長岡市に佇むカフェ『樹林館』🌳☕️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍴肴家 信清🍷...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 家系ラーメン武将家　浅草店
+10月5日にオープンした『家系らーめん...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍽️【特別な日のご褒美に】...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 和牛焼肉としお
+🥩和牛焼肉の新境地へ— 🥩...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍜日々“育てる”一杯、ここにあり🔥...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷✨クオリティ高×価格安×lowkeyな接客✨🍴...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: インプラント治療なら「上志津中央歯科」🌟...</t>
+  </si>
+  <si>
+    <t>recently_completed</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 中洲にあるミュージックカラオケバー！Food持ち込み可🍴🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🔥【香り豊かな炭火焼と多彩な日本酒が楽しめる！】🔥...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: んにちは！【Mont Blanc】です🍸✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟SUNRISEガールズバー｜豊田市山之手🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🏡☕canurip Cafe☕🏡
+茨木に佇む韓国風古民家カフェღ...</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍻 鉄板居酒屋こぐま 🔥
+🏡 アットホームな空間で、心もお腹も大満足！...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 至福のひとときを、すすきの 蟹一 で。
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶 合同会社 大和・北海道の幸とお酒 たかふじ 🐟
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨ 天ぷら むらやま｜吉祥寺 ✨
+ゆったりとした カウンター席...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 遠心太助 – 新発想の洗浄ツールで塗装コスト削減！ 🌍
+🔹...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 pikku onni 🍽️
+🐟 北海道の海の恵み ×...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉処 縁結び｜鮮度抜群の極上焼肉 🥩...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🎤 カラオケサーカス 調布店 🎪✨
+東京・調布市の音楽オアシス！🌆🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟大林歯科医院｜千葉県美浜区幕張西🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟栄駅から徒歩2分の歯医者【日生歯科診療所】🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟府中市の歯医者【たかすぎ歯科クリニック】🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟かわらもと歯科｜大阪市・吹田市🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍻【リーズナブルにたくさん食べたいなら「居酒屋一（ichi）」】🍻...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨【国分町に新しい刺激を！】✨
+「Extreme Bar...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌻季節の食材を使った心温まるお料理とお酒🌻...</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟【焼鳥の真髄、ここにあり】🌟
+「焼鳥酒場...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌙【川越の夜をおしゃれに楽しむならここ！】🌙
+「AMUSEMENT Bar...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🐾✨ Heart Dog ✨🐶
+ドッグカフェ 庵（いおり） OPEN！...</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【髙橋歯科】
+“噛み合わせ”から整える、お口とカラダのトータルケア🪥...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍽️【リラックスしたひとときを「HIDEOUT」で】🍷...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🔥 ホルモン 焼肉 楽丸...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩✨ステーキTaka✨🥩...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🔥 炭火焼とり 隼...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 えびすバル –自家製ローストビーフと自然派ワインのマリアージュを🥩...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨ 高岡市のバー【NUTS】へようこそ！🍹...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍽️ おるたなキッチン – カフェみたいな定食屋で心ほっこりごはん時間☕🍱...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: LEAP SPORTS GYMで、一緒に成長しよう！💪🔥
+🏋️‍♂️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌴 Manly Australian Cafe ＆ Bar 🇦🇺
+📍...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦌🦪 鹿肉＆オイスターバル SLOW...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🎤✨ snack &amp; karaoke bar Belle 🍸🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶✨ 居酒屋1484（イシバシ） 🍽️🎣
+📍 大宮駅東口から徒歩すぐ！
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍁 旬彩和食よし田 🍁
+📍 つくば市の本格和食店
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌿 HATASU 🌱
+植物と暮らそう。
+何気ない日常に 緑...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 肉とワインのイタリアン酒場 more 前橋店 🥩
+📍...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 肉とワインのイタリアン酒場 more 高崎店 🥩
+📍...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥢 中華バル Chiry - チャイリー 🍻
+📍...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🎉【スナックバー Reina 求人募集】🎉...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉 からし亭 東高円寺店 🍽...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉 からし亭 新高円寺店 🍽...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥢【とんかつ樹｜こだわり抜いた食材と空間で味わう極上のひととき】🥢...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉 からし亭 経堂店 🔥
+〜...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 炭火焼肉 からし亭 八戸店 🥢
+〜...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉 からし亭 三沢店 🍚✨
+〜...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟 2024年9月、津田沼にNEW OPEN！🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦷【地域密着！いつでも安心のかかりつけ歯科】...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦷【日野市で予防歯科なら！】...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨【透明感のある白い歯を目指して】✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🎵✨ BAR EIT8で特別なひと時を✨🎵...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨【求人募集】✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦷【船橋市で理想の口元へ】🦷
+医療法人社団哲の子会...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶居酒屋ちるとSake 三軒茶屋店✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦷✨ チロル歯科 ✨🦷...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】🥋✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍽️✨...</t>
+  </si>
+  <si>
+    <t>2026-12-28</t>
+  </si>
+  <si>
+    <t>Instagram投稿: "洋食ビストロコパンへようこそ！ハンバーグが自慢の喫茶店です🍔✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: "🍸 ＆ジン 🍸
+バーテンダー監修のカジュアルなジン酒場✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: もちもちの魔法で心もお腹も満たす✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨arphills✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【韓国酒場 チィヘッソ】🇰🇷🔥...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌍スパイス香る夜の冒険へ🍷
+【muy bien｜ムイビエン】...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨気になる歯並び、今こそ治しましょう✨...</t>
+  </si>
+  <si>
+    <t>2027-02-02</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌼bague total beautyへようこそ🌼...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🎤スナックよりみち🎤...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🦷✨岡田歯科医院✨🦷...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍町寿司いちもんめ｜福井市大手...</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【すし嘉まさ】🍣✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【すし嘉まさ】新しい仲間を募集しています！🍣✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【鮨一花】🍣✨
+豊水すすきの駅から徒歩1分🚶‍♂️🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 「SEA DROP Roast...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨2024年9月20日 NEW OPEN✨
+Hairsalon...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 株式会社 TechVoice・FRETTA 🍸
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📢 株式会社 TechVoice・FRETTA スタッフ募集中！ 🍸
+✨...</t>
+  </si>
+  <si>
+    <t>2026-04-03</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>初回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Instagram</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>投稿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">: 🦷 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>海岸歯科室｜インビザライン矯正
+「見えない矯正で、理想の笑顔へ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>✨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>...</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>ショカイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -421,6 +896,19 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
@@ -446,9 +934,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -750,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y62"/>
+  <dimension ref="A1:Y171"/>
   <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -5120,6 +5611,7682 @@
       </c>
       <c r="Y62">
         <v>226.8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
+        <v>127</v>
+      </c>
+      <c r="D63" t="s">
+        <v>87</v>
+      </c>
+      <c r="E63" t="s">
+        <v>29</v>
+      </c>
+      <c r="F63">
+        <v>125</v>
+      </c>
+      <c r="G63" t="s">
+        <v>39</v>
+      </c>
+      <c r="H63">
+        <v>5341</v>
+      </c>
+      <c r="I63">
+        <v>1.5070209999999999</v>
+      </c>
+      <c r="J63">
+        <v>35.24</v>
+      </c>
+      <c r="K63">
+        <v>160</v>
+      </c>
+      <c r="L63" t="s">
+        <v>30</v>
+      </c>
+      <c r="M63">
+        <v>4405</v>
+      </c>
+      <c r="N63" t="s">
+        <v>128</v>
+      </c>
+      <c r="O63">
+        <v>8049</v>
+      </c>
+      <c r="P63">
+        <v>547.27295300000003</v>
+      </c>
+      <c r="Q63">
+        <v>125</v>
+      </c>
+      <c r="S63">
+        <v>35.24</v>
+      </c>
+      <c r="T63">
+        <v>1.552988</v>
+      </c>
+      <c r="U63">
+        <v>234</v>
+      </c>
+      <c r="V63">
+        <v>2.9071929999999999</v>
+      </c>
+      <c r="W63">
+        <v>18.824786</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" t="s">
+        <v>129</v>
+      </c>
+      <c r="D64" t="s">
+        <v>87</v>
+      </c>
+      <c r="E64" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64">
+        <v>92</v>
+      </c>
+      <c r="G64" t="s">
+        <v>39</v>
+      </c>
+      <c r="H64">
+        <v>2591</v>
+      </c>
+      <c r="I64">
+        <v>1.654188</v>
+      </c>
+      <c r="J64">
+        <v>47.815217390000001</v>
+      </c>
+      <c r="K64">
+        <v>160</v>
+      </c>
+      <c r="L64" t="s">
+        <v>30</v>
+      </c>
+      <c r="M64">
+        <v>4399</v>
+      </c>
+      <c r="N64" t="s">
+        <v>130</v>
+      </c>
+      <c r="O64">
+        <v>4286</v>
+      </c>
+      <c r="P64">
+        <v>1026.3649089999999</v>
+      </c>
+      <c r="Q64">
+        <v>92</v>
+      </c>
+      <c r="S64">
+        <v>47.815216999999997</v>
+      </c>
+      <c r="T64">
+        <v>2.1465239999999999</v>
+      </c>
+      <c r="U64">
+        <v>106</v>
+      </c>
+      <c r="V64">
+        <v>2.4731679999999998</v>
+      </c>
+      <c r="W64">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" t="s">
+        <v>131</v>
+      </c>
+      <c r="D65" t="s">
+        <v>87</v>
+      </c>
+      <c r="E65" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65">
+        <v>140</v>
+      </c>
+      <c r="G65" t="s">
+        <v>39</v>
+      </c>
+      <c r="H65">
+        <v>5227</v>
+      </c>
+      <c r="I65">
+        <v>1.4746509999999999</v>
+      </c>
+      <c r="J65">
+        <v>31.442857140000001</v>
+      </c>
+      <c r="K65">
+        <v>160</v>
+      </c>
+      <c r="L65" t="s">
+        <v>30</v>
+      </c>
+      <c r="M65">
+        <v>4402</v>
+      </c>
+      <c r="N65" t="s">
+        <v>132</v>
+      </c>
+      <c r="O65">
+        <v>7708</v>
+      </c>
+      <c r="P65">
+        <v>571.094966</v>
+      </c>
+      <c r="Q65">
+        <v>140</v>
+      </c>
+      <c r="S65">
+        <v>31.442857</v>
+      </c>
+      <c r="T65">
+        <v>1.816295</v>
+      </c>
+      <c r="U65">
+        <v>252</v>
+      </c>
+      <c r="V65">
+        <v>3.2693310000000002</v>
+      </c>
+      <c r="W65">
+        <v>17.468254000000002</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>25</v>
+      </c>
+      <c r="B66" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" t="s">
+        <v>133</v>
+      </c>
+      <c r="D66" t="s">
+        <v>87</v>
+      </c>
+      <c r="E66" t="s">
+        <v>29</v>
+      </c>
+      <c r="F66">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s">
+        <v>39</v>
+      </c>
+      <c r="H66">
+        <v>1707</v>
+      </c>
+      <c r="I66">
+        <v>1.287639</v>
+      </c>
+      <c r="J66">
+        <v>56.358974359999998</v>
+      </c>
+      <c r="K66">
+        <v>160</v>
+      </c>
+      <c r="L66" t="s">
+        <v>30</v>
+      </c>
+      <c r="M66">
+        <v>4396</v>
+      </c>
+      <c r="N66" t="s">
+        <v>132</v>
+      </c>
+      <c r="O66">
+        <v>2198</v>
+      </c>
+      <c r="P66">
+        <v>2000</v>
+      </c>
+      <c r="Q66">
+        <v>78</v>
+      </c>
+      <c r="S66">
+        <v>56.358974000000003</v>
+      </c>
+      <c r="T66">
+        <v>3.5486810000000002</v>
+      </c>
+      <c r="U66">
+        <v>81</v>
+      </c>
+      <c r="V66">
+        <v>3.685168</v>
+      </c>
+      <c r="W66">
+        <v>54.271605000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" t="s">
+        <v>134</v>
+      </c>
+      <c r="D67" t="s">
+        <v>87</v>
+      </c>
+      <c r="E67" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67">
+        <v>209</v>
+      </c>
+      <c r="G67" t="s">
+        <v>39</v>
+      </c>
+      <c r="H67">
+        <v>4032</v>
+      </c>
+      <c r="I67">
+        <v>1.678571</v>
+      </c>
+      <c r="J67">
+        <v>20.971291870000002</v>
+      </c>
+      <c r="K67">
+        <v>160</v>
+      </c>
+      <c r="L67" t="s">
+        <v>30</v>
+      </c>
+      <c r="M67">
+        <v>4383</v>
+      </c>
+      <c r="N67" t="s">
+        <v>132</v>
+      </c>
+      <c r="O67">
+        <v>6768</v>
+      </c>
+      <c r="P67">
+        <v>647.60638300000005</v>
+      </c>
+      <c r="Q67">
+        <v>209</v>
+      </c>
+      <c r="S67">
+        <v>20.971291999999998</v>
+      </c>
+      <c r="T67">
+        <v>3.0880610000000002</v>
+      </c>
+      <c r="U67">
+        <v>299</v>
+      </c>
+      <c r="V67">
+        <v>4.4178490000000004</v>
+      </c>
+      <c r="W67">
+        <v>14.658863</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" t="s">
+        <v>135</v>
+      </c>
+      <c r="D68" t="s">
+        <v>87</v>
+      </c>
+      <c r="E68" t="s">
+        <v>29</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="K68" t="s">
+        <v>34</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68" t="s">
+        <v>136</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>25</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" t="s">
+        <v>137</v>
+      </c>
+      <c r="D69" t="s">
+        <v>87</v>
+      </c>
+      <c r="E69" t="s">
+        <v>29</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="K69" t="s">
+        <v>34</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69" t="s">
+        <v>136</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+      <c r="U69">
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" t="s">
+        <v>138</v>
+      </c>
+      <c r="D70" t="s">
+        <v>87</v>
+      </c>
+      <c r="E70" t="s">
+        <v>29</v>
+      </c>
+      <c r="F70">
+        <v>148</v>
+      </c>
+      <c r="G70" t="s">
+        <v>39</v>
+      </c>
+      <c r="H70">
+        <v>4017</v>
+      </c>
+      <c r="I70">
+        <v>1.456809</v>
+      </c>
+      <c r="J70">
+        <v>30.64189189</v>
+      </c>
+      <c r="K70" t="s">
+        <v>34</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>4535</v>
+      </c>
+      <c r="N70" t="s">
+        <v>35</v>
+      </c>
+      <c r="O70">
+        <v>5852</v>
+      </c>
+      <c r="P70">
+        <v>774.94873500000006</v>
+      </c>
+      <c r="Q70">
+        <v>148</v>
+      </c>
+      <c r="S70">
+        <v>30.641891999999999</v>
+      </c>
+      <c r="T70">
+        <v>2.5290499999999998</v>
+      </c>
+      <c r="U70">
+        <v>191</v>
+      </c>
+      <c r="V70">
+        <v>3.2638410000000002</v>
+      </c>
+      <c r="W70">
+        <v>23.743455999999998</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>25</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" t="s">
+        <v>139</v>
+      </c>
+      <c r="D71" t="s">
+        <v>87</v>
+      </c>
+      <c r="E71" t="s">
+        <v>29</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="K71" t="s">
+        <v>34</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71" t="s">
+        <v>136</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>25</v>
+      </c>
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" t="s">
+        <v>140</v>
+      </c>
+      <c r="D72" t="s">
+        <v>87</v>
+      </c>
+      <c r="E72" t="s">
+        <v>29</v>
+      </c>
+      <c r="F72">
+        <v>386</v>
+      </c>
+      <c r="G72" t="s">
+        <v>39</v>
+      </c>
+      <c r="H72">
+        <v>5269</v>
+      </c>
+      <c r="I72">
+        <v>1.2602009999999999</v>
+      </c>
+      <c r="J72">
+        <v>12.007772020000001</v>
+      </c>
+      <c r="K72" t="s">
+        <v>34</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>4635</v>
+      </c>
+      <c r="N72" t="s">
+        <v>35</v>
+      </c>
+      <c r="O72">
+        <v>6640</v>
+      </c>
+      <c r="P72">
+        <v>698.04216899999994</v>
+      </c>
+      <c r="Q72">
+        <v>386</v>
+      </c>
+      <c r="S72">
+        <v>12.007771999999999</v>
+      </c>
+      <c r="T72">
+        <v>5.8132529999999996</v>
+      </c>
+      <c r="U72">
+        <v>434</v>
+      </c>
+      <c r="V72">
+        <v>6.5361450000000003</v>
+      </c>
+      <c r="W72">
+        <v>10.679724</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" t="s">
+        <v>141</v>
+      </c>
+      <c r="D73" t="s">
+        <v>87</v>
+      </c>
+      <c r="E73" t="s">
+        <v>29</v>
+      </c>
+      <c r="F73">
+        <v>192</v>
+      </c>
+      <c r="G73" t="s">
+        <v>39</v>
+      </c>
+      <c r="H73">
+        <v>5602</v>
+      </c>
+      <c r="I73">
+        <v>1.365227</v>
+      </c>
+      <c r="J73">
+        <v>23.4375</v>
+      </c>
+      <c r="K73" t="s">
+        <v>34</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>4500</v>
+      </c>
+      <c r="N73" t="s">
+        <v>35</v>
+      </c>
+      <c r="O73">
+        <v>7648</v>
+      </c>
+      <c r="P73">
+        <v>588.38912100000005</v>
+      </c>
+      <c r="Q73">
+        <v>192</v>
+      </c>
+      <c r="S73">
+        <v>23.4375</v>
+      </c>
+      <c r="T73">
+        <v>2.5104600000000001</v>
+      </c>
+      <c r="U73">
+        <v>249</v>
+      </c>
+      <c r="V73">
+        <v>3.2557529999999999</v>
+      </c>
+      <c r="W73">
+        <v>18.072289000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" t="s">
+        <v>142</v>
+      </c>
+      <c r="D74" t="s">
+        <v>87</v>
+      </c>
+      <c r="E74" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74">
+        <v>126</v>
+      </c>
+      <c r="G74" t="s">
+        <v>39</v>
+      </c>
+      <c r="H74">
+        <v>2880</v>
+      </c>
+      <c r="I74">
+        <v>1.629861</v>
+      </c>
+      <c r="J74">
+        <v>39.888888889999997</v>
+      </c>
+      <c r="K74" t="s">
+        <v>34</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>5026</v>
+      </c>
+      <c r="N74" t="s">
+        <v>35</v>
+      </c>
+      <c r="O74">
+        <v>4694</v>
+      </c>
+      <c r="P74">
+        <v>1070.7285899999999</v>
+      </c>
+      <c r="Q74">
+        <v>126</v>
+      </c>
+      <c r="S74">
+        <v>39.888888999999999</v>
+      </c>
+      <c r="T74">
+        <v>2.6842779999999999</v>
+      </c>
+      <c r="U74">
+        <v>155</v>
+      </c>
+      <c r="V74">
+        <v>3.3020879999999999</v>
+      </c>
+      <c r="W74">
+        <v>32.425806000000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>25</v>
+      </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" t="s">
+        <v>143</v>
+      </c>
+      <c r="D75" t="s">
+        <v>87</v>
+      </c>
+      <c r="E75" t="s">
+        <v>29</v>
+      </c>
+      <c r="F75">
+        <v>274</v>
+      </c>
+      <c r="G75" t="s">
+        <v>39</v>
+      </c>
+      <c r="H75">
+        <v>5278</v>
+      </c>
+      <c r="I75">
+        <v>1.2415689999999999</v>
+      </c>
+      <c r="J75">
+        <v>16.412408760000002</v>
+      </c>
+      <c r="K75" t="s">
+        <v>34</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>4497</v>
+      </c>
+      <c r="N75" t="s">
+        <v>89</v>
+      </c>
+      <c r="O75">
+        <v>6553</v>
+      </c>
+      <c r="P75">
+        <v>686.25057200000003</v>
+      </c>
+      <c r="Q75">
+        <v>274</v>
+      </c>
+      <c r="S75">
+        <v>16.412409</v>
+      </c>
+      <c r="T75">
+        <v>4.1812909999999999</v>
+      </c>
+      <c r="U75">
+        <v>301</v>
+      </c>
+      <c r="V75">
+        <v>4.5933159999999997</v>
+      </c>
+      <c r="W75">
+        <v>14.940199</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>25</v>
+      </c>
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" t="s">
+        <v>144</v>
+      </c>
+      <c r="D76" t="s">
+        <v>87</v>
+      </c>
+      <c r="E76" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76">
+        <v>320</v>
+      </c>
+      <c r="G76" t="s">
+        <v>39</v>
+      </c>
+      <c r="H76">
+        <v>3927</v>
+      </c>
+      <c r="I76">
+        <v>1.441813</v>
+      </c>
+      <c r="J76">
+        <v>13.731249999999999</v>
+      </c>
+      <c r="K76">
+        <v>160</v>
+      </c>
+      <c r="L76" t="s">
+        <v>30</v>
+      </c>
+      <c r="M76">
+        <v>4394</v>
+      </c>
+      <c r="N76" t="s">
+        <v>85</v>
+      </c>
+      <c r="O76">
+        <v>5662</v>
+      </c>
+      <c r="P76">
+        <v>776.05086500000004</v>
+      </c>
+      <c r="Q76">
+        <v>320</v>
+      </c>
+      <c r="S76">
+        <v>13.731249999999999</v>
+      </c>
+      <c r="T76">
+        <v>5.651713</v>
+      </c>
+      <c r="U76">
+        <v>353</v>
+      </c>
+      <c r="V76">
+        <v>6.2345459999999999</v>
+      </c>
+      <c r="W76">
+        <v>12.447592</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>25</v>
+      </c>
+      <c r="B77" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" t="s">
+        <v>145</v>
+      </c>
+      <c r="D77" t="s">
+        <v>87</v>
+      </c>
+      <c r="E77" t="s">
+        <v>29</v>
+      </c>
+      <c r="F77">
+        <v>135</v>
+      </c>
+      <c r="G77" t="s">
+        <v>39</v>
+      </c>
+      <c r="H77">
+        <v>3543</v>
+      </c>
+      <c r="I77">
+        <v>1.224386</v>
+      </c>
+      <c r="J77">
+        <v>32.637037040000003</v>
+      </c>
+      <c r="K77">
+        <v>160</v>
+      </c>
+      <c r="L77" t="s">
+        <v>30</v>
+      </c>
+      <c r="M77">
+        <v>4406</v>
+      </c>
+      <c r="N77" t="s">
+        <v>146</v>
+      </c>
+      <c r="O77">
+        <v>4338</v>
+      </c>
+      <c r="P77">
+        <v>1015.675426</v>
+      </c>
+      <c r="Q77">
+        <v>135</v>
+      </c>
+      <c r="S77">
+        <v>32.637036999999999</v>
+      </c>
+      <c r="T77">
+        <v>3.1120329999999998</v>
+      </c>
+      <c r="U77">
+        <v>168</v>
+      </c>
+      <c r="V77">
+        <v>3.8727520000000002</v>
+      </c>
+      <c r="W77">
+        <v>26.226189999999999</v>
+      </c>
+      <c r="X77">
+        <v>119</v>
+      </c>
+      <c r="Y77">
+        <v>37.025210000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" t="s">
+        <v>147</v>
+      </c>
+      <c r="D78" t="s">
+        <v>87</v>
+      </c>
+      <c r="E78" t="s">
+        <v>29</v>
+      </c>
+      <c r="F78">
+        <v>267</v>
+      </c>
+      <c r="G78" t="s">
+        <v>39</v>
+      </c>
+      <c r="H78">
+        <v>3041</v>
+      </c>
+      <c r="I78">
+        <v>1.626439</v>
+      </c>
+      <c r="J78">
+        <v>16.46067416</v>
+      </c>
+      <c r="K78">
+        <v>160</v>
+      </c>
+      <c r="L78" t="s">
+        <v>30</v>
+      </c>
+      <c r="M78">
+        <v>4395</v>
+      </c>
+      <c r="N78" t="s">
+        <v>148</v>
+      </c>
+      <c r="O78">
+        <v>4946</v>
+      </c>
+      <c r="P78">
+        <v>888.59684600000003</v>
+      </c>
+      <c r="Q78">
+        <v>267</v>
+      </c>
+      <c r="S78">
+        <v>16.460674000000001</v>
+      </c>
+      <c r="T78">
+        <v>5.3983020000000002</v>
+      </c>
+      <c r="U78">
+        <v>289</v>
+      </c>
+      <c r="V78">
+        <v>5.8431059999999997</v>
+      </c>
+      <c r="W78">
+        <v>15.207611999999999</v>
+      </c>
+      <c r="X78">
+        <v>227</v>
+      </c>
+      <c r="Y78">
+        <v>19.361232999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" t="s">
+        <v>149</v>
+      </c>
+      <c r="D79" t="s">
+        <v>87</v>
+      </c>
+      <c r="E79" t="s">
+        <v>29</v>
+      </c>
+      <c r="F79">
+        <v>217</v>
+      </c>
+      <c r="G79" t="s">
+        <v>39</v>
+      </c>
+      <c r="H79">
+        <v>5134</v>
+      </c>
+      <c r="I79">
+        <v>1.2197119999999999</v>
+      </c>
+      <c r="J79">
+        <v>20.25345622</v>
+      </c>
+      <c r="K79">
+        <v>160</v>
+      </c>
+      <c r="L79" t="s">
+        <v>30</v>
+      </c>
+      <c r="M79">
+        <v>4395</v>
+      </c>
+      <c r="N79" t="s">
+        <v>148</v>
+      </c>
+      <c r="O79">
+        <v>6262</v>
+      </c>
+      <c r="P79">
+        <v>701.85244299999999</v>
+      </c>
+      <c r="Q79">
+        <v>217</v>
+      </c>
+      <c r="S79">
+        <v>20.253456</v>
+      </c>
+      <c r="T79">
+        <v>3.465347</v>
+      </c>
+      <c r="U79">
+        <v>267</v>
+      </c>
+      <c r="V79">
+        <v>4.2638129999999999</v>
+      </c>
+      <c r="W79">
+        <v>16.460674000000001</v>
+      </c>
+      <c r="X79">
+        <v>198</v>
+      </c>
+      <c r="Y79">
+        <v>22.19697</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" t="s">
+        <v>150</v>
+      </c>
+      <c r="D80" t="s">
+        <v>87</v>
+      </c>
+      <c r="E80" t="s">
+        <v>29</v>
+      </c>
+      <c r="F80">
+        <v>202</v>
+      </c>
+      <c r="G80" t="s">
+        <v>39</v>
+      </c>
+      <c r="H80">
+        <v>4645</v>
+      </c>
+      <c r="I80">
+        <v>1.5773950000000001</v>
+      </c>
+      <c r="J80">
+        <v>21.846534649999999</v>
+      </c>
+      <c r="K80">
+        <v>160</v>
+      </c>
+      <c r="L80" t="s">
+        <v>30</v>
+      </c>
+      <c r="M80">
+        <v>4413</v>
+      </c>
+      <c r="N80" t="s">
+        <v>148</v>
+      </c>
+      <c r="O80">
+        <v>7327</v>
+      </c>
+      <c r="P80">
+        <v>602.29288899999995</v>
+      </c>
+      <c r="Q80">
+        <v>202</v>
+      </c>
+      <c r="S80">
+        <v>21.846534999999999</v>
+      </c>
+      <c r="T80">
+        <v>2.756926</v>
+      </c>
+      <c r="U80">
+        <v>279</v>
+      </c>
+      <c r="V80">
+        <v>3.8078340000000002</v>
+      </c>
+      <c r="W80">
+        <v>15.817204</v>
+      </c>
+      <c r="X80">
+        <v>8</v>
+      </c>
+      <c r="Y80">
+        <v>551.625</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>25</v>
+      </c>
+      <c r="B81" t="s">
+        <v>26</v>
+      </c>
+      <c r="C81" t="s">
+        <v>151</v>
+      </c>
+      <c r="D81" t="s">
+        <v>87</v>
+      </c>
+      <c r="E81" t="s">
+        <v>29</v>
+      </c>
+      <c r="F81">
+        <v>199</v>
+      </c>
+      <c r="G81" t="s">
+        <v>39</v>
+      </c>
+      <c r="H81">
+        <v>4068</v>
+      </c>
+      <c r="I81">
+        <v>1.506637</v>
+      </c>
+      <c r="J81">
+        <v>22.226130650000002</v>
+      </c>
+      <c r="K81">
+        <v>160</v>
+      </c>
+      <c r="L81" t="s">
+        <v>30</v>
+      </c>
+      <c r="M81">
+        <v>4423</v>
+      </c>
+      <c r="N81" t="s">
+        <v>148</v>
+      </c>
+      <c r="O81">
+        <v>6129</v>
+      </c>
+      <c r="P81">
+        <v>721.65116699999999</v>
+      </c>
+      <c r="Q81">
+        <v>199</v>
+      </c>
+      <c r="S81">
+        <v>22.226130999999999</v>
+      </c>
+      <c r="T81">
+        <v>3.2468590000000002</v>
+      </c>
+      <c r="U81">
+        <v>259</v>
+      </c>
+      <c r="V81">
+        <v>4.2258120000000003</v>
+      </c>
+      <c r="W81">
+        <v>17.077220000000001</v>
+      </c>
+      <c r="X81">
+        <v>6</v>
+      </c>
+      <c r="Y81">
+        <v>737.16666699999996</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>25</v>
+      </c>
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
+        <v>152</v>
+      </c>
+      <c r="D82" t="s">
+        <v>87</v>
+      </c>
+      <c r="E82" t="s">
+        <v>29</v>
+      </c>
+      <c r="F82">
+        <v>348</v>
+      </c>
+      <c r="G82" t="s">
+        <v>39</v>
+      </c>
+      <c r="H82">
+        <v>6754</v>
+      </c>
+      <c r="I82">
+        <v>1.3036719999999999</v>
+      </c>
+      <c r="J82">
+        <v>12.66091954</v>
+      </c>
+      <c r="K82">
+        <v>160</v>
+      </c>
+      <c r="L82" t="s">
+        <v>30</v>
+      </c>
+      <c r="M82">
+        <v>4406</v>
+      </c>
+      <c r="N82" t="s">
+        <v>148</v>
+      </c>
+      <c r="O82">
+        <v>8805</v>
+      </c>
+      <c r="P82">
+        <v>500.39750099999998</v>
+      </c>
+      <c r="Q82">
+        <v>348</v>
+      </c>
+      <c r="S82">
+        <v>12.660920000000001</v>
+      </c>
+      <c r="T82">
+        <v>3.9523000000000001</v>
+      </c>
+      <c r="U82">
+        <v>421</v>
+      </c>
+      <c r="V82">
+        <v>4.7813739999999996</v>
+      </c>
+      <c r="W82">
+        <v>10.465558</v>
+      </c>
+      <c r="X82">
+        <v>348</v>
+      </c>
+      <c r="Y82">
+        <v>12.660920000000001</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83" t="s">
+        <v>26</v>
+      </c>
+      <c r="C83" t="s">
+        <v>153</v>
+      </c>
+      <c r="D83" t="s">
+        <v>87</v>
+      </c>
+      <c r="E83" t="s">
+        <v>29</v>
+      </c>
+      <c r="F83">
+        <v>371</v>
+      </c>
+      <c r="G83" t="s">
+        <v>39</v>
+      </c>
+      <c r="H83">
+        <v>7283</v>
+      </c>
+      <c r="I83">
+        <v>1.207195</v>
+      </c>
+      <c r="J83">
+        <v>11.86792453</v>
+      </c>
+      <c r="K83">
+        <v>160</v>
+      </c>
+      <c r="L83" t="s">
+        <v>30</v>
+      </c>
+      <c r="M83">
+        <v>4403</v>
+      </c>
+      <c r="N83" t="s">
+        <v>148</v>
+      </c>
+      <c r="O83">
+        <v>8792</v>
+      </c>
+      <c r="P83">
+        <v>500.796178</v>
+      </c>
+      <c r="Q83">
+        <v>371</v>
+      </c>
+      <c r="S83">
+        <v>11.867925</v>
+      </c>
+      <c r="T83">
+        <v>4.2197449999999996</v>
+      </c>
+      <c r="U83">
+        <v>479</v>
+      </c>
+      <c r="V83">
+        <v>5.4481349999999997</v>
+      </c>
+      <c r="W83">
+        <v>9.1920669999999998</v>
+      </c>
+      <c r="X83">
+        <v>377</v>
+      </c>
+      <c r="Y83">
+        <v>11.679045</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>25</v>
+      </c>
+      <c r="B84" t="s">
+        <v>26</v>
+      </c>
+      <c r="C84" t="s">
+        <v>154</v>
+      </c>
+      <c r="D84" t="s">
+        <v>87</v>
+      </c>
+      <c r="E84" t="s">
+        <v>29</v>
+      </c>
+      <c r="F84">
+        <v>79</v>
+      </c>
+      <c r="G84" t="s">
+        <v>39</v>
+      </c>
+      <c r="H84">
+        <v>2196</v>
+      </c>
+      <c r="I84">
+        <v>1.6648449999999999</v>
+      </c>
+      <c r="J84">
+        <v>55.72151899</v>
+      </c>
+      <c r="K84">
+        <v>160</v>
+      </c>
+      <c r="L84" t="s">
+        <v>30</v>
+      </c>
+      <c r="M84">
+        <v>4402</v>
+      </c>
+      <c r="N84" t="s">
+        <v>148</v>
+      </c>
+      <c r="O84">
+        <v>3656</v>
+      </c>
+      <c r="P84">
+        <v>1204.0481400000001</v>
+      </c>
+      <c r="Q84">
+        <v>79</v>
+      </c>
+      <c r="S84">
+        <v>55.721519000000001</v>
+      </c>
+      <c r="T84">
+        <v>2.1608320000000001</v>
+      </c>
+      <c r="U84">
+        <v>79</v>
+      </c>
+      <c r="V84">
+        <v>2.1608320000000001</v>
+      </c>
+      <c r="W84">
+        <v>55.721519000000001</v>
+      </c>
+      <c r="X84">
+        <v>67</v>
+      </c>
+      <c r="Y84">
+        <v>65.701492999999999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>25</v>
+      </c>
+      <c r="B85" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" t="s">
+        <v>155</v>
+      </c>
+      <c r="D85" t="s">
+        <v>87</v>
+      </c>
+      <c r="E85" t="s">
+        <v>29</v>
+      </c>
+      <c r="F85">
+        <v>668</v>
+      </c>
+      <c r="G85" t="s">
+        <v>39</v>
+      </c>
+      <c r="H85">
+        <v>10118</v>
+      </c>
+      <c r="I85">
+        <v>1.156849</v>
+      </c>
+      <c r="J85">
+        <v>6.5748502999999996</v>
+      </c>
+      <c r="K85">
+        <v>160</v>
+      </c>
+      <c r="L85" t="s">
+        <v>30</v>
+      </c>
+      <c r="M85">
+        <v>4392</v>
+      </c>
+      <c r="N85" t="s">
+        <v>148</v>
+      </c>
+      <c r="O85">
+        <v>11705</v>
+      </c>
+      <c r="P85">
+        <v>375.22426300000001</v>
+      </c>
+      <c r="Q85">
+        <v>668</v>
+      </c>
+      <c r="S85">
+        <v>6.5748499999999996</v>
+      </c>
+      <c r="T85">
+        <v>5.706963</v>
+      </c>
+      <c r="U85">
+        <v>753</v>
+      </c>
+      <c r="V85">
+        <v>6.4331480000000001</v>
+      </c>
+      <c r="W85">
+        <v>5.8326690000000001</v>
+      </c>
+      <c r="X85">
+        <v>566</v>
+      </c>
+      <c r="Y85">
+        <v>7.7597170000000002</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B86" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" t="s">
+        <v>156</v>
+      </c>
+      <c r="D86" t="s">
+        <v>87</v>
+      </c>
+      <c r="E86" t="s">
+        <v>29</v>
+      </c>
+      <c r="F86">
+        <v>272</v>
+      </c>
+      <c r="G86" t="s">
+        <v>39</v>
+      </c>
+      <c r="H86">
+        <v>4227</v>
+      </c>
+      <c r="I86">
+        <v>1.2460370000000001</v>
+      </c>
+      <c r="J86">
+        <v>16.14338235</v>
+      </c>
+      <c r="K86">
+        <v>160</v>
+      </c>
+      <c r="L86" t="s">
+        <v>30</v>
+      </c>
+      <c r="M86">
+        <v>4391</v>
+      </c>
+      <c r="N86" t="s">
+        <v>148</v>
+      </c>
+      <c r="O86">
+        <v>5267</v>
+      </c>
+      <c r="P86">
+        <v>833.68141300000002</v>
+      </c>
+      <c r="Q86">
+        <v>272</v>
+      </c>
+      <c r="S86">
+        <v>16.143381999999999</v>
+      </c>
+      <c r="T86">
+        <v>5.1642299999999999</v>
+      </c>
+      <c r="U86">
+        <v>277</v>
+      </c>
+      <c r="V86">
+        <v>5.2591609999999998</v>
+      </c>
+      <c r="W86">
+        <v>15.851986</v>
+      </c>
+      <c r="X86">
+        <v>47</v>
+      </c>
+      <c r="Y86">
+        <v>93.425532000000004</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" t="s">
+        <v>26</v>
+      </c>
+      <c r="C87" t="s">
+        <v>157</v>
+      </c>
+      <c r="D87" t="s">
+        <v>87</v>
+      </c>
+      <c r="E87" t="s">
+        <v>29</v>
+      </c>
+      <c r="F87">
+        <v>200</v>
+      </c>
+      <c r="G87" t="s">
+        <v>39</v>
+      </c>
+      <c r="H87">
+        <v>5798</v>
+      </c>
+      <c r="I87">
+        <v>1.345291</v>
+      </c>
+      <c r="J87">
+        <v>22.045000000000002</v>
+      </c>
+      <c r="K87">
+        <v>160</v>
+      </c>
+      <c r="L87" t="s">
+        <v>30</v>
+      </c>
+      <c r="M87">
+        <v>4409</v>
+      </c>
+      <c r="N87" t="s">
+        <v>148</v>
+      </c>
+      <c r="O87">
+        <v>7800</v>
+      </c>
+      <c r="P87">
+        <v>565.25640999999996</v>
+      </c>
+      <c r="Q87">
+        <v>200</v>
+      </c>
+      <c r="S87">
+        <v>22.045000000000002</v>
+      </c>
+      <c r="T87">
+        <v>2.5641029999999998</v>
+      </c>
+      <c r="U87">
+        <v>257</v>
+      </c>
+      <c r="V87">
+        <v>3.2948719999999998</v>
+      </c>
+      <c r="W87">
+        <v>17.155642</v>
+      </c>
+      <c r="X87">
+        <v>198</v>
+      </c>
+      <c r="Y87">
+        <v>22.267676999999999</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>25</v>
+      </c>
+      <c r="B88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" t="s">
+        <v>158</v>
+      </c>
+      <c r="D88" t="s">
+        <v>87</v>
+      </c>
+      <c r="E88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88">
+        <v>79</v>
+      </c>
+      <c r="G88" t="s">
+        <v>39</v>
+      </c>
+      <c r="H88">
+        <v>4532</v>
+      </c>
+      <c r="I88">
+        <v>1.4170339999999999</v>
+      </c>
+      <c r="J88">
+        <v>55.468354429999998</v>
+      </c>
+      <c r="K88">
+        <v>160</v>
+      </c>
+      <c r="L88" t="s">
+        <v>30</v>
+      </c>
+      <c r="M88">
+        <v>4382</v>
+      </c>
+      <c r="N88" t="s">
+        <v>148</v>
+      </c>
+      <c r="O88">
+        <v>6422</v>
+      </c>
+      <c r="P88">
+        <v>682.34195</v>
+      </c>
+      <c r="Q88">
+        <v>79</v>
+      </c>
+      <c r="S88">
+        <v>55.468353999999998</v>
+      </c>
+      <c r="T88">
+        <v>1.230146</v>
+      </c>
+      <c r="U88">
+        <v>102</v>
+      </c>
+      <c r="V88">
+        <v>1.58829</v>
+      </c>
+      <c r="W88">
+        <v>42.960783999999997</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" t="s">
+        <v>159</v>
+      </c>
+      <c r="D89" t="s">
+        <v>87</v>
+      </c>
+      <c r="E89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F89">
+        <v>397</v>
+      </c>
+      <c r="G89" t="s">
+        <v>39</v>
+      </c>
+      <c r="H89">
+        <v>5824</v>
+      </c>
+      <c r="I89">
+        <v>1.172218</v>
+      </c>
+      <c r="J89">
+        <v>11.062972289999999</v>
+      </c>
+      <c r="K89">
+        <v>160</v>
+      </c>
+      <c r="L89" t="s">
+        <v>30</v>
+      </c>
+      <c r="M89">
+        <v>4392</v>
+      </c>
+      <c r="N89" t="s">
+        <v>148</v>
+      </c>
+      <c r="O89">
+        <v>6827</v>
+      </c>
+      <c r="P89">
+        <v>643.32796299999995</v>
+      </c>
+      <c r="Q89">
+        <v>397</v>
+      </c>
+      <c r="S89">
+        <v>11.062972</v>
+      </c>
+      <c r="T89">
+        <v>5.8151460000000004</v>
+      </c>
+      <c r="U89">
+        <v>494</v>
+      </c>
+      <c r="V89">
+        <v>7.2359749999999998</v>
+      </c>
+      <c r="W89">
+        <v>8.8906880000000008</v>
+      </c>
+      <c r="X89">
+        <v>410</v>
+      </c>
+      <c r="Y89">
+        <v>10.712194999999999</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B90" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" t="s">
+        <v>160</v>
+      </c>
+      <c r="D90" t="s">
+        <v>161</v>
+      </c>
+      <c r="E90" t="s">
+        <v>29</v>
+      </c>
+      <c r="F90">
+        <v>163</v>
+      </c>
+      <c r="G90" t="s">
+        <v>39</v>
+      </c>
+      <c r="H90">
+        <v>2204</v>
+      </c>
+      <c r="I90">
+        <v>1.2377499999999999</v>
+      </c>
+      <c r="J90">
+        <v>26.950920249999999</v>
+      </c>
+      <c r="K90">
+        <v>160</v>
+      </c>
+      <c r="L90" t="s">
+        <v>30</v>
+      </c>
+      <c r="M90">
+        <v>4393</v>
+      </c>
+      <c r="N90" t="s">
+        <v>99</v>
+      </c>
+      <c r="O90">
+        <v>2728</v>
+      </c>
+      <c r="P90">
+        <v>1610.3372429999999</v>
+      </c>
+      <c r="Q90">
+        <v>163</v>
+      </c>
+      <c r="S90">
+        <v>26.95092</v>
+      </c>
+      <c r="T90">
+        <v>5.9750730000000001</v>
+      </c>
+      <c r="U90">
+        <v>173</v>
+      </c>
+      <c r="V90">
+        <v>6.3416420000000002</v>
+      </c>
+      <c r="W90">
+        <v>25.393063999999999</v>
+      </c>
+      <c r="X90">
+        <v>126</v>
+      </c>
+      <c r="Y90">
+        <v>34.865079000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91" t="s">
+        <v>162</v>
+      </c>
+      <c r="D91" t="s">
+        <v>38</v>
+      </c>
+      <c r="E91" t="s">
+        <v>29</v>
+      </c>
+      <c r="F91">
+        <v>146</v>
+      </c>
+      <c r="G91" t="s">
+        <v>39</v>
+      </c>
+      <c r="H91">
+        <v>3455</v>
+      </c>
+      <c r="I91">
+        <v>1.2989869999999999</v>
+      </c>
+      <c r="J91">
+        <v>30.157534250000001</v>
+      </c>
+      <c r="K91">
+        <v>160</v>
+      </c>
+      <c r="L91" t="s">
+        <v>30</v>
+      </c>
+      <c r="M91">
+        <v>4403</v>
+      </c>
+      <c r="N91" t="s">
+        <v>103</v>
+      </c>
+      <c r="O91">
+        <v>4488</v>
+      </c>
+      <c r="P91">
+        <v>981.06060600000001</v>
+      </c>
+      <c r="Q91">
+        <v>146</v>
+      </c>
+      <c r="S91">
+        <v>30.157533999999998</v>
+      </c>
+      <c r="T91">
+        <v>3.2531189999999999</v>
+      </c>
+      <c r="U91">
+        <v>163</v>
+      </c>
+      <c r="V91">
+        <v>3.631907</v>
+      </c>
+      <c r="W91">
+        <v>27.012270000000001</v>
+      </c>
+      <c r="X91">
+        <v>18</v>
+      </c>
+      <c r="Y91">
+        <v>244.61111099999999</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>25</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" t="s">
+        <v>162</v>
+      </c>
+      <c r="D92" t="s">
+        <v>38</v>
+      </c>
+      <c r="E92" t="s">
+        <v>29</v>
+      </c>
+      <c r="F92">
+        <v>196</v>
+      </c>
+      <c r="G92" t="s">
+        <v>39</v>
+      </c>
+      <c r="H92">
+        <v>3948</v>
+      </c>
+      <c r="I92">
+        <v>1.337893</v>
+      </c>
+      <c r="J92">
+        <v>22.474489800000001</v>
+      </c>
+      <c r="K92">
+        <v>160</v>
+      </c>
+      <c r="L92" t="s">
+        <v>30</v>
+      </c>
+      <c r="M92">
+        <v>4405</v>
+      </c>
+      <c r="N92" t="s">
+        <v>103</v>
+      </c>
+      <c r="O92">
+        <v>5282</v>
+      </c>
+      <c r="P92">
+        <v>833.96440700000005</v>
+      </c>
+      <c r="Q92">
+        <v>196</v>
+      </c>
+      <c r="S92">
+        <v>22.474489999999999</v>
+      </c>
+      <c r="T92">
+        <v>3.7107160000000001</v>
+      </c>
+      <c r="U92">
+        <v>241</v>
+      </c>
+      <c r="V92">
+        <v>4.5626660000000001</v>
+      </c>
+      <c r="W92">
+        <v>18.278008</v>
+      </c>
+      <c r="X92">
+        <v>176</v>
+      </c>
+      <c r="Y92">
+        <v>25.028409</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>25</v>
+      </c>
+      <c r="B93" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" t="s">
+        <v>163</v>
+      </c>
+      <c r="D93" t="s">
+        <v>38</v>
+      </c>
+      <c r="E93" t="s">
+        <v>29</v>
+      </c>
+      <c r="F93">
+        <v>238</v>
+      </c>
+      <c r="G93" t="s">
+        <v>39</v>
+      </c>
+      <c r="H93">
+        <v>3058</v>
+      </c>
+      <c r="I93">
+        <v>1.576848</v>
+      </c>
+      <c r="J93">
+        <v>18.546218490000001</v>
+      </c>
+      <c r="K93">
+        <v>160</v>
+      </c>
+      <c r="L93" t="s">
+        <v>30</v>
+      </c>
+      <c r="M93">
+        <v>4414</v>
+      </c>
+      <c r="N93" t="s">
+        <v>103</v>
+      </c>
+      <c r="O93">
+        <v>4822</v>
+      </c>
+      <c r="P93">
+        <v>915.38780599999996</v>
+      </c>
+      <c r="Q93">
+        <v>238</v>
+      </c>
+      <c r="S93">
+        <v>18.546218</v>
+      </c>
+      <c r="T93">
+        <v>4.9357110000000004</v>
+      </c>
+      <c r="U93">
+        <v>251</v>
+      </c>
+      <c r="V93">
+        <v>5.2053089999999997</v>
+      </c>
+      <c r="W93">
+        <v>17.585657000000001</v>
+      </c>
+      <c r="X93">
+        <v>192</v>
+      </c>
+      <c r="Y93">
+        <v>22.989583</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>25</v>
+      </c>
+      <c r="B94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" t="s">
+        <v>164</v>
+      </c>
+      <c r="D94" t="s">
+        <v>38</v>
+      </c>
+      <c r="E94" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94">
+        <v>174</v>
+      </c>
+      <c r="G94" t="s">
+        <v>39</v>
+      </c>
+      <c r="H94">
+        <v>3555</v>
+      </c>
+      <c r="I94">
+        <v>1.3625879999999999</v>
+      </c>
+      <c r="J94">
+        <v>25.281609199999998</v>
+      </c>
+      <c r="K94">
+        <v>160</v>
+      </c>
+      <c r="L94" t="s">
+        <v>30</v>
+      </c>
+      <c r="M94">
+        <v>4399</v>
+      </c>
+      <c r="N94" t="s">
+        <v>103</v>
+      </c>
+      <c r="O94">
+        <v>4844</v>
+      </c>
+      <c r="P94">
+        <v>908.13377400000002</v>
+      </c>
+      <c r="Q94">
+        <v>174</v>
+      </c>
+      <c r="S94">
+        <v>25.281609</v>
+      </c>
+      <c r="T94">
+        <v>3.5920730000000001</v>
+      </c>
+      <c r="U94">
+        <v>273</v>
+      </c>
+      <c r="V94">
+        <v>5.6358379999999997</v>
+      </c>
+      <c r="W94">
+        <v>16.113553</v>
+      </c>
+      <c r="X94">
+        <v>208</v>
+      </c>
+      <c r="Y94">
+        <v>21.149038000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>25</v>
+      </c>
+      <c r="B95" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95" t="s">
+        <v>165</v>
+      </c>
+      <c r="D95" t="s">
+        <v>38</v>
+      </c>
+      <c r="E95" t="s">
+        <v>29</v>
+      </c>
+      <c r="F95">
+        <v>218</v>
+      </c>
+      <c r="G95" t="s">
+        <v>39</v>
+      </c>
+      <c r="H95">
+        <v>5389</v>
+      </c>
+      <c r="I95">
+        <v>1.381518</v>
+      </c>
+      <c r="J95">
+        <v>20.201834860000002</v>
+      </c>
+      <c r="K95">
+        <v>160</v>
+      </c>
+      <c r="L95" t="s">
+        <v>30</v>
+      </c>
+      <c r="M95">
+        <v>4404</v>
+      </c>
+      <c r="N95" t="s">
+        <v>103</v>
+      </c>
+      <c r="O95">
+        <v>7445</v>
+      </c>
+      <c r="P95">
+        <v>591.53794500000004</v>
+      </c>
+      <c r="Q95">
+        <v>218</v>
+      </c>
+      <c r="S95">
+        <v>20.201834999999999</v>
+      </c>
+      <c r="T95">
+        <v>2.92814</v>
+      </c>
+      <c r="U95">
+        <v>308</v>
+      </c>
+      <c r="V95">
+        <v>4.1370050000000003</v>
+      </c>
+      <c r="W95">
+        <v>14.298700999999999</v>
+      </c>
+      <c r="X95">
+        <v>238</v>
+      </c>
+      <c r="Y95">
+        <v>18.504201999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>25</v>
+      </c>
+      <c r="B96" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96" t="s">
+        <v>166</v>
+      </c>
+      <c r="D96" t="s">
+        <v>38</v>
+      </c>
+      <c r="E96" t="s">
+        <v>29</v>
+      </c>
+      <c r="F96">
+        <v>449</v>
+      </c>
+      <c r="G96" t="s">
+        <v>39</v>
+      </c>
+      <c r="H96">
+        <v>2984</v>
+      </c>
+      <c r="I96">
+        <v>1.401475</v>
+      </c>
+      <c r="J96">
+        <v>9.8173719399999992</v>
+      </c>
+      <c r="K96">
+        <v>160</v>
+      </c>
+      <c r="L96" t="s">
+        <v>30</v>
+      </c>
+      <c r="M96">
+        <v>4408</v>
+      </c>
+      <c r="N96" t="s">
+        <v>167</v>
+      </c>
+      <c r="O96">
+        <v>4182</v>
+      </c>
+      <c r="P96">
+        <v>1054.041129</v>
+      </c>
+      <c r="Q96">
+        <v>449</v>
+      </c>
+      <c r="S96">
+        <v>9.8173720000000007</v>
+      </c>
+      <c r="T96">
+        <v>10.73649</v>
+      </c>
+      <c r="U96">
+        <v>535</v>
+      </c>
+      <c r="V96">
+        <v>12.792922000000001</v>
+      </c>
+      <c r="W96">
+        <v>8.2392520000000005</v>
+      </c>
+      <c r="X96">
+        <v>7</v>
+      </c>
+      <c r="Y96">
+        <v>629.71428600000002</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>25</v>
+      </c>
+      <c r="B97" t="s">
+        <v>26</v>
+      </c>
+      <c r="C97" t="s">
+        <v>168</v>
+      </c>
+      <c r="D97" t="s">
+        <v>38</v>
+      </c>
+      <c r="E97" t="s">
+        <v>29</v>
+      </c>
+      <c r="F97">
+        <v>89</v>
+      </c>
+      <c r="G97" t="s">
+        <v>39</v>
+      </c>
+      <c r="H97">
+        <v>2637</v>
+      </c>
+      <c r="I97">
+        <v>2.0830489999999999</v>
+      </c>
+      <c r="J97">
+        <v>49.426966290000003</v>
+      </c>
+      <c r="K97">
+        <v>160</v>
+      </c>
+      <c r="L97" t="s">
+        <v>30</v>
+      </c>
+      <c r="M97">
+        <v>4399</v>
+      </c>
+      <c r="N97" t="s">
+        <v>103</v>
+      </c>
+      <c r="O97">
+        <v>5493</v>
+      </c>
+      <c r="P97">
+        <v>800.83742900000004</v>
+      </c>
+      <c r="Q97">
+        <v>89</v>
+      </c>
+      <c r="S97">
+        <v>49.426966</v>
+      </c>
+      <c r="T97">
+        <v>1.620244</v>
+      </c>
+      <c r="U97">
+        <v>115</v>
+      </c>
+      <c r="V97">
+        <v>2.0935739999999998</v>
+      </c>
+      <c r="W97">
+        <v>38.252173999999997</v>
+      </c>
+      <c r="X97">
+        <v>86</v>
+      </c>
+      <c r="Y97">
+        <v>51.151162999999997</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>25</v>
+      </c>
+      <c r="B98" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98" t="s">
+        <v>169</v>
+      </c>
+      <c r="D98" t="s">
+        <v>38</v>
+      </c>
+      <c r="E98" t="s">
+        <v>29</v>
+      </c>
+      <c r="F98">
+        <v>182</v>
+      </c>
+      <c r="G98" t="s">
+        <v>39</v>
+      </c>
+      <c r="H98">
+        <v>2350</v>
+      </c>
+      <c r="I98">
+        <v>1.5421279999999999</v>
+      </c>
+      <c r="J98">
+        <v>24.164835159999999</v>
+      </c>
+      <c r="K98">
+        <v>160</v>
+      </c>
+      <c r="L98" t="s">
+        <v>30</v>
+      </c>
+      <c r="M98">
+        <v>4398</v>
+      </c>
+      <c r="N98" t="s">
+        <v>103</v>
+      </c>
+      <c r="O98">
+        <v>3624</v>
+      </c>
+      <c r="P98">
+        <v>1213.576159</v>
+      </c>
+      <c r="Q98">
+        <v>182</v>
+      </c>
+      <c r="S98">
+        <v>24.164835</v>
+      </c>
+      <c r="T98">
+        <v>5.0220750000000001</v>
+      </c>
+      <c r="U98">
+        <v>194</v>
+      </c>
+      <c r="V98">
+        <v>5.3532010000000003</v>
+      </c>
+      <c r="W98">
+        <v>22.670103000000001</v>
+      </c>
+      <c r="X98">
+        <v>169</v>
+      </c>
+      <c r="Y98">
+        <v>26.023669000000002</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>25</v>
+      </c>
+      <c r="B99" t="s">
+        <v>26</v>
+      </c>
+      <c r="C99" t="s">
+        <v>170</v>
+      </c>
+      <c r="D99" t="s">
+        <v>38</v>
+      </c>
+      <c r="E99" t="s">
+        <v>29</v>
+      </c>
+      <c r="F99">
+        <v>335</v>
+      </c>
+      <c r="G99" t="s">
+        <v>39</v>
+      </c>
+      <c r="H99">
+        <v>5364</v>
+      </c>
+      <c r="I99">
+        <v>1.339485</v>
+      </c>
+      <c r="J99">
+        <v>13.16716418</v>
+      </c>
+      <c r="K99">
+        <v>160</v>
+      </c>
+      <c r="L99" t="s">
+        <v>30</v>
+      </c>
+      <c r="M99">
+        <v>4411</v>
+      </c>
+      <c r="N99" t="s">
+        <v>103</v>
+      </c>
+      <c r="O99">
+        <v>7185</v>
+      </c>
+      <c r="P99">
+        <v>613.91788399999996</v>
+      </c>
+      <c r="Q99">
+        <v>335</v>
+      </c>
+      <c r="S99">
+        <v>13.167164</v>
+      </c>
+      <c r="T99">
+        <v>4.6624910000000002</v>
+      </c>
+      <c r="U99">
+        <v>388</v>
+      </c>
+      <c r="V99">
+        <v>5.4001390000000002</v>
+      </c>
+      <c r="W99">
+        <v>11.368556999999999</v>
+      </c>
+      <c r="X99">
+        <v>340</v>
+      </c>
+      <c r="Y99">
+        <v>12.973528999999999</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>25</v>
+      </c>
+      <c r="B100" t="s">
+        <v>26</v>
+      </c>
+      <c r="C100" t="s">
+        <v>171</v>
+      </c>
+      <c r="D100" t="s">
+        <v>38</v>
+      </c>
+      <c r="E100" t="s">
+        <v>29</v>
+      </c>
+      <c r="F100">
+        <v>653</v>
+      </c>
+      <c r="G100" t="s">
+        <v>39</v>
+      </c>
+      <c r="H100">
+        <v>4275</v>
+      </c>
+      <c r="I100">
+        <v>1.2718130000000001</v>
+      </c>
+      <c r="J100">
+        <v>6.7320061300000003</v>
+      </c>
+      <c r="K100">
+        <v>160</v>
+      </c>
+      <c r="L100" t="s">
+        <v>30</v>
+      </c>
+      <c r="M100">
+        <v>4396</v>
+      </c>
+      <c r="N100" t="s">
+        <v>103</v>
+      </c>
+      <c r="O100">
+        <v>5437</v>
+      </c>
+      <c r="P100">
+        <v>808.53411800000003</v>
+      </c>
+      <c r="Q100">
+        <v>653</v>
+      </c>
+      <c r="S100">
+        <v>6.7320060000000002</v>
+      </c>
+      <c r="T100">
+        <v>12.010300000000001</v>
+      </c>
+      <c r="U100">
+        <v>681</v>
+      </c>
+      <c r="V100">
+        <v>12.52529</v>
+      </c>
+      <c r="W100">
+        <v>6.4552129999999996</v>
+      </c>
+      <c r="X100">
+        <v>589</v>
+      </c>
+      <c r="Y100">
+        <v>7.4634970000000003</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>25</v>
+      </c>
+      <c r="B101" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" t="s">
+        <v>172</v>
+      </c>
+      <c r="D101" t="s">
+        <v>38</v>
+      </c>
+      <c r="E101" t="s">
+        <v>29</v>
+      </c>
+      <c r="F101">
+        <v>251</v>
+      </c>
+      <c r="G101" t="s">
+        <v>39</v>
+      </c>
+      <c r="H101">
+        <v>4291</v>
+      </c>
+      <c r="I101">
+        <v>1.150082</v>
+      </c>
+      <c r="J101">
+        <v>17.537848610000001</v>
+      </c>
+      <c r="K101">
+        <v>160</v>
+      </c>
+      <c r="L101" t="s">
+        <v>30</v>
+      </c>
+      <c r="M101">
+        <v>4402</v>
+      </c>
+      <c r="N101" t="s">
+        <v>103</v>
+      </c>
+      <c r="O101">
+        <v>4935</v>
+      </c>
+      <c r="P101">
+        <v>891.995947</v>
+      </c>
+      <c r="Q101">
+        <v>251</v>
+      </c>
+      <c r="S101">
+        <v>17.537849000000001</v>
+      </c>
+      <c r="T101">
+        <v>5.0861200000000002</v>
+      </c>
+      <c r="U101">
+        <v>259</v>
+      </c>
+      <c r="V101">
+        <v>5.248227</v>
+      </c>
+      <c r="W101">
+        <v>16.996138999999999</v>
+      </c>
+      <c r="X101">
+        <v>121</v>
+      </c>
+      <c r="Y101">
+        <v>36.380164999999998</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>25</v>
+      </c>
+      <c r="B102" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" t="s">
+        <v>173</v>
+      </c>
+      <c r="D102" t="s">
+        <v>38</v>
+      </c>
+      <c r="E102" t="s">
+        <v>29</v>
+      </c>
+      <c r="F102">
+        <v>423</v>
+      </c>
+      <c r="G102" t="s">
+        <v>39</v>
+      </c>
+      <c r="H102">
+        <v>5414</v>
+      </c>
+      <c r="I102">
+        <v>1.404876</v>
+      </c>
+      <c r="J102">
+        <v>10.408983449999999</v>
+      </c>
+      <c r="K102">
+        <v>160</v>
+      </c>
+      <c r="L102" t="s">
+        <v>30</v>
+      </c>
+      <c r="M102">
+        <v>4403</v>
+      </c>
+      <c r="N102" t="s">
+        <v>103</v>
+      </c>
+      <c r="O102">
+        <v>7606</v>
+      </c>
+      <c r="P102">
+        <v>578.88509099999999</v>
+      </c>
+      <c r="Q102">
+        <v>423</v>
+      </c>
+      <c r="S102">
+        <v>10.408982999999999</v>
+      </c>
+      <c r="T102">
+        <v>5.5613989999999998</v>
+      </c>
+      <c r="U102">
+        <v>512</v>
+      </c>
+      <c r="V102">
+        <v>6.731528</v>
+      </c>
+      <c r="W102">
+        <v>8.5996089999999992</v>
+      </c>
+      <c r="X102">
+        <v>405</v>
+      </c>
+      <c r="Y102">
+        <v>10.871605000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>25</v>
+      </c>
+      <c r="B103" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103" t="s">
+        <v>174</v>
+      </c>
+      <c r="D103" t="s">
+        <v>38</v>
+      </c>
+      <c r="E103" t="s">
+        <v>29</v>
+      </c>
+      <c r="F103">
+        <v>227</v>
+      </c>
+      <c r="G103" t="s">
+        <v>39</v>
+      </c>
+      <c r="H103">
+        <v>3010</v>
+      </c>
+      <c r="I103">
+        <v>1.4066449999999999</v>
+      </c>
+      <c r="J103">
+        <v>19.418502199999999</v>
+      </c>
+      <c r="K103">
+        <v>160</v>
+      </c>
+      <c r="L103" t="s">
+        <v>30</v>
+      </c>
+      <c r="M103">
+        <v>4408</v>
+      </c>
+      <c r="N103" t="s">
+        <v>103</v>
+      </c>
+      <c r="O103">
+        <v>4234</v>
+      </c>
+      <c r="P103">
+        <v>1041.0958900000001</v>
+      </c>
+      <c r="Q103">
+        <v>227</v>
+      </c>
+      <c r="S103">
+        <v>19.418502</v>
+      </c>
+      <c r="T103">
+        <v>5.3613600000000003</v>
+      </c>
+      <c r="U103">
+        <v>264</v>
+      </c>
+      <c r="V103">
+        <v>6.235239</v>
+      </c>
+      <c r="W103">
+        <v>16.69697</v>
+      </c>
+      <c r="X103">
+        <v>227</v>
+      </c>
+      <c r="Y103">
+        <v>19.418502</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>25</v>
+      </c>
+      <c r="B104" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" t="s">
+        <v>175</v>
+      </c>
+      <c r="D104" t="s">
+        <v>38</v>
+      </c>
+      <c r="E104" t="s">
+        <v>29</v>
+      </c>
+      <c r="F104">
+        <v>145</v>
+      </c>
+      <c r="G104" t="s">
+        <v>39</v>
+      </c>
+      <c r="H104">
+        <v>5373</v>
+      </c>
+      <c r="I104">
+        <v>1.195422</v>
+      </c>
+      <c r="J104">
+        <v>30.344827590000001</v>
+      </c>
+      <c r="K104">
+        <v>160</v>
+      </c>
+      <c r="L104" t="s">
+        <v>30</v>
+      </c>
+      <c r="M104">
+        <v>4400</v>
+      </c>
+      <c r="N104" t="s">
+        <v>103</v>
+      </c>
+      <c r="O104">
+        <v>6423</v>
+      </c>
+      <c r="P104">
+        <v>685.03814399999999</v>
+      </c>
+      <c r="Q104">
+        <v>145</v>
+      </c>
+      <c r="S104">
+        <v>30.344828</v>
+      </c>
+      <c r="T104">
+        <v>2.2575120000000002</v>
+      </c>
+      <c r="U104">
+        <v>192</v>
+      </c>
+      <c r="V104">
+        <v>2.9892569999999998</v>
+      </c>
+      <c r="W104">
+        <v>22.916667</v>
+      </c>
+      <c r="X104">
+        <v>116</v>
+      </c>
+      <c r="Y104">
+        <v>37.931033999999997</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>25</v>
+      </c>
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" t="s">
+        <v>176</v>
+      </c>
+      <c r="D105" t="s">
+        <v>28</v>
+      </c>
+      <c r="E105" t="s">
+        <v>29</v>
+      </c>
+      <c r="F105">
+        <v>149</v>
+      </c>
+      <c r="G105" t="s">
+        <v>39</v>
+      </c>
+      <c r="H105">
+        <v>2573</v>
+      </c>
+      <c r="I105">
+        <v>1.394093</v>
+      </c>
+      <c r="J105">
+        <v>29.41610738</v>
+      </c>
+      <c r="K105">
+        <v>160</v>
+      </c>
+      <c r="L105" t="s">
+        <v>30</v>
+      </c>
+      <c r="M105">
+        <v>4383</v>
+      </c>
+      <c r="N105" t="s">
+        <v>103</v>
+      </c>
+      <c r="O105">
+        <v>3587</v>
+      </c>
+      <c r="P105">
+        <v>1221.912462</v>
+      </c>
+      <c r="Q105">
+        <v>149</v>
+      </c>
+      <c r="S105">
+        <v>29.416107</v>
+      </c>
+      <c r="T105">
+        <v>4.1538890000000004</v>
+      </c>
+      <c r="U105">
+        <v>166</v>
+      </c>
+      <c r="V105">
+        <v>4.6278230000000002</v>
+      </c>
+      <c r="W105">
+        <v>26.403614000000001</v>
+      </c>
+      <c r="X105">
+        <v>132</v>
+      </c>
+      <c r="Y105">
+        <v>33.204545000000003</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>25</v>
+      </c>
+      <c r="B106" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" t="s">
+        <v>177</v>
+      </c>
+      <c r="D106" t="s">
+        <v>28</v>
+      </c>
+      <c r="E106" t="s">
+        <v>29</v>
+      </c>
+      <c r="F106">
+        <v>112</v>
+      </c>
+      <c r="G106" t="s">
+        <v>39</v>
+      </c>
+      <c r="H106">
+        <v>2288</v>
+      </c>
+      <c r="I106">
+        <v>1.21722</v>
+      </c>
+      <c r="J106">
+        <v>39.330357139999997</v>
+      </c>
+      <c r="K106">
+        <v>160</v>
+      </c>
+      <c r="L106" t="s">
+        <v>30</v>
+      </c>
+      <c r="M106">
+        <v>4405</v>
+      </c>
+      <c r="N106" t="s">
+        <v>103</v>
+      </c>
+      <c r="O106">
+        <v>2785</v>
+      </c>
+      <c r="P106">
+        <v>1581.6876119999999</v>
+      </c>
+      <c r="Q106">
+        <v>112</v>
+      </c>
+      <c r="S106">
+        <v>39.330356999999999</v>
+      </c>
+      <c r="T106">
+        <v>4.0215439999999996</v>
+      </c>
+      <c r="U106">
+        <v>113</v>
+      </c>
+      <c r="V106">
+        <v>4.0574510000000004</v>
+      </c>
+      <c r="W106">
+        <v>38.982301</v>
+      </c>
+      <c r="X106">
+        <v>84</v>
+      </c>
+      <c r="Y106">
+        <v>52.440475999999997</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>25</v>
+      </c>
+      <c r="B107" t="s">
+        <v>26</v>
+      </c>
+      <c r="C107" t="s">
+        <v>178</v>
+      </c>
+      <c r="D107" t="s">
+        <v>38</v>
+      </c>
+      <c r="E107" t="s">
+        <v>29</v>
+      </c>
+      <c r="F107">
+        <v>96</v>
+      </c>
+      <c r="G107" t="s">
+        <v>39</v>
+      </c>
+      <c r="H107">
+        <v>2088</v>
+      </c>
+      <c r="I107">
+        <v>1.220785</v>
+      </c>
+      <c r="J107">
+        <v>45.583333330000002</v>
+      </c>
+      <c r="K107">
+        <v>160</v>
+      </c>
+      <c r="L107" t="s">
+        <v>30</v>
+      </c>
+      <c r="M107">
+        <v>4376</v>
+      </c>
+      <c r="N107" t="s">
+        <v>103</v>
+      </c>
+      <c r="O107">
+        <v>2549</v>
+      </c>
+      <c r="P107">
+        <v>1716.751667</v>
+      </c>
+      <c r="Q107">
+        <v>96</v>
+      </c>
+      <c r="S107">
+        <v>45.583333000000003</v>
+      </c>
+      <c r="T107">
+        <v>3.7661829999999998</v>
+      </c>
+      <c r="U107">
+        <v>108</v>
+      </c>
+      <c r="V107">
+        <v>4.2369560000000002</v>
+      </c>
+      <c r="W107">
+        <v>40.518518999999998</v>
+      </c>
+      <c r="X107">
+        <v>74</v>
+      </c>
+      <c r="Y107">
+        <v>59.135134999999998</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>25</v>
+      </c>
+      <c r="B108" t="s">
+        <v>26</v>
+      </c>
+      <c r="C108" t="s">
+        <v>179</v>
+      </c>
+      <c r="D108" t="s">
+        <v>38</v>
+      </c>
+      <c r="E108" t="s">
+        <v>29</v>
+      </c>
+      <c r="F108">
+        <v>152</v>
+      </c>
+      <c r="G108" t="s">
+        <v>39</v>
+      </c>
+      <c r="H108">
+        <v>2418</v>
+      </c>
+      <c r="I108">
+        <v>1.343259</v>
+      </c>
+      <c r="J108">
+        <v>28.96710526</v>
+      </c>
+      <c r="K108">
+        <v>160</v>
+      </c>
+      <c r="L108" t="s">
+        <v>30</v>
+      </c>
+      <c r="M108">
+        <v>4403</v>
+      </c>
+      <c r="N108" t="s">
+        <v>103</v>
+      </c>
+      <c r="O108">
+        <v>3248</v>
+      </c>
+      <c r="P108">
+        <v>1355.6034480000001</v>
+      </c>
+      <c r="Q108">
+        <v>152</v>
+      </c>
+      <c r="S108">
+        <v>28.967105</v>
+      </c>
+      <c r="T108">
+        <v>4.6798029999999997</v>
+      </c>
+      <c r="U108">
+        <v>167</v>
+      </c>
+      <c r="V108">
+        <v>5.1416259999999996</v>
+      </c>
+      <c r="W108">
+        <v>26.365269000000001</v>
+      </c>
+      <c r="X108">
+        <v>129</v>
+      </c>
+      <c r="Y108">
+        <v>34.131782999999999</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>25</v>
+      </c>
+      <c r="B109" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109" t="s">
+        <v>180</v>
+      </c>
+      <c r="D109" t="s">
+        <v>38</v>
+      </c>
+      <c r="E109" t="s">
+        <v>29</v>
+      </c>
+      <c r="F109">
+        <v>205</v>
+      </c>
+      <c r="G109" t="s">
+        <v>39</v>
+      </c>
+      <c r="H109">
+        <v>4291</v>
+      </c>
+      <c r="I109">
+        <v>1.505943</v>
+      </c>
+      <c r="J109">
+        <v>21.468292680000001</v>
+      </c>
+      <c r="K109">
+        <v>160</v>
+      </c>
+      <c r="L109" t="s">
+        <v>30</v>
+      </c>
+      <c r="M109">
+        <v>4401</v>
+      </c>
+      <c r="N109" t="s">
+        <v>103</v>
+      </c>
+      <c r="O109">
+        <v>6462</v>
+      </c>
+      <c r="P109">
+        <v>681.05849599999999</v>
+      </c>
+      <c r="Q109">
+        <v>205</v>
+      </c>
+      <c r="S109">
+        <v>21.468292999999999</v>
+      </c>
+      <c r="T109">
+        <v>3.1723919999999999</v>
+      </c>
+      <c r="U109">
+        <v>250</v>
+      </c>
+      <c r="V109">
+        <v>3.8687710000000002</v>
+      </c>
+      <c r="W109">
+        <v>17.603999999999999</v>
+      </c>
+      <c r="X109">
+        <v>201</v>
+      </c>
+      <c r="Y109">
+        <v>21.895522</v>
+      </c>
+    </row>
+    <row r="110" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>25</v>
+      </c>
+      <c r="B110" t="s">
+        <v>26</v>
+      </c>
+      <c r="C110" t="s">
+        <v>181</v>
+      </c>
+      <c r="D110" t="s">
+        <v>38</v>
+      </c>
+      <c r="E110" t="s">
+        <v>29</v>
+      </c>
+      <c r="F110">
+        <v>150</v>
+      </c>
+      <c r="G110" t="s">
+        <v>39</v>
+      </c>
+      <c r="H110">
+        <v>4434</v>
+      </c>
+      <c r="I110">
+        <v>1.2866489999999999</v>
+      </c>
+      <c r="J110">
+        <v>29.333333329999999</v>
+      </c>
+      <c r="K110">
+        <v>160</v>
+      </c>
+      <c r="L110" t="s">
+        <v>30</v>
+      </c>
+      <c r="M110">
+        <v>4400</v>
+      </c>
+      <c r="N110" t="s">
+        <v>103</v>
+      </c>
+      <c r="O110">
+        <v>5705</v>
+      </c>
+      <c r="P110">
+        <v>771.253287</v>
+      </c>
+      <c r="Q110">
+        <v>150</v>
+      </c>
+      <c r="S110">
+        <v>29.333333</v>
+      </c>
+      <c r="T110">
+        <v>2.629273</v>
+      </c>
+      <c r="U110">
+        <v>172</v>
+      </c>
+      <c r="V110">
+        <v>3.0148990000000002</v>
+      </c>
+      <c r="W110">
+        <v>25.581395000000001</v>
+      </c>
+      <c r="X110">
+        <v>139</v>
+      </c>
+      <c r="Y110">
+        <v>31.654675999999998</v>
+      </c>
+    </row>
+    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>25</v>
+      </c>
+      <c r="B111" t="s">
+        <v>26</v>
+      </c>
+      <c r="C111" t="s">
+        <v>182</v>
+      </c>
+      <c r="D111" t="s">
+        <v>38</v>
+      </c>
+      <c r="E111" t="s">
+        <v>29</v>
+      </c>
+      <c r="F111">
+        <v>208</v>
+      </c>
+      <c r="G111" t="s">
+        <v>39</v>
+      </c>
+      <c r="H111">
+        <v>2270</v>
+      </c>
+      <c r="I111">
+        <v>1.613656</v>
+      </c>
+      <c r="J111">
+        <v>21.20192308</v>
+      </c>
+      <c r="K111">
+        <v>160</v>
+      </c>
+      <c r="L111" t="s">
+        <v>30</v>
+      </c>
+      <c r="M111">
+        <v>4410</v>
+      </c>
+      <c r="N111" t="s">
+        <v>183</v>
+      </c>
+      <c r="O111">
+        <v>3663</v>
+      </c>
+      <c r="P111">
+        <v>1203.931204</v>
+      </c>
+      <c r="Q111">
+        <v>208</v>
+      </c>
+      <c r="S111">
+        <v>21.201923000000001</v>
+      </c>
+      <c r="T111">
+        <v>5.6784059999999998</v>
+      </c>
+      <c r="U111">
+        <v>225</v>
+      </c>
+      <c r="V111">
+        <v>6.142506</v>
+      </c>
+      <c r="W111">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="X111">
+        <v>21</v>
+      </c>
+      <c r="Y111">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>25</v>
+      </c>
+      <c r="B112" t="s">
+        <v>26</v>
+      </c>
+      <c r="C112" t="s">
+        <v>184</v>
+      </c>
+      <c r="D112" t="s">
+        <v>38</v>
+      </c>
+      <c r="E112" t="s">
+        <v>29</v>
+      </c>
+      <c r="F112">
+        <v>274</v>
+      </c>
+      <c r="G112" t="s">
+        <v>39</v>
+      </c>
+      <c r="H112">
+        <v>3397</v>
+      </c>
+      <c r="I112">
+        <v>1.5275240000000001</v>
+      </c>
+      <c r="J112">
+        <v>16.054744530000001</v>
+      </c>
+      <c r="K112">
+        <v>160</v>
+      </c>
+      <c r="L112" t="s">
+        <v>30</v>
+      </c>
+      <c r="M112">
+        <v>4399</v>
+      </c>
+      <c r="N112" t="s">
+        <v>183</v>
+      </c>
+      <c r="O112">
+        <v>5189</v>
+      </c>
+      <c r="P112">
+        <v>847.75486599999999</v>
+      </c>
+      <c r="Q112">
+        <v>274</v>
+      </c>
+      <c r="S112">
+        <v>16.054745</v>
+      </c>
+      <c r="T112">
+        <v>5.2804010000000003</v>
+      </c>
+      <c r="U112">
+        <v>305</v>
+      </c>
+      <c r="V112">
+        <v>5.8778180000000004</v>
+      </c>
+      <c r="W112">
+        <v>14.422950999999999</v>
+      </c>
+      <c r="X112">
+        <v>12</v>
+      </c>
+      <c r="Y112">
+        <v>366.58333299999998</v>
+      </c>
+    </row>
+    <row r="113" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B113" t="s">
+        <v>26</v>
+      </c>
+      <c r="C113" t="s">
+        <v>185</v>
+      </c>
+      <c r="D113" t="s">
+        <v>38</v>
+      </c>
+      <c r="E113" t="s">
+        <v>29</v>
+      </c>
+      <c r="F113">
+        <v>146</v>
+      </c>
+      <c r="G113" t="s">
+        <v>39</v>
+      </c>
+      <c r="H113">
+        <v>4478</v>
+      </c>
+      <c r="I113">
+        <v>1.1471640000000001</v>
+      </c>
+      <c r="J113">
+        <v>30.047945210000002</v>
+      </c>
+      <c r="K113">
+        <v>160</v>
+      </c>
+      <c r="L113" t="s">
+        <v>30</v>
+      </c>
+      <c r="M113">
+        <v>4387</v>
+      </c>
+      <c r="N113" t="s">
+        <v>183</v>
+      </c>
+      <c r="O113">
+        <v>5137</v>
+      </c>
+      <c r="P113">
+        <v>854.00038900000004</v>
+      </c>
+      <c r="Q113">
+        <v>146</v>
+      </c>
+      <c r="S113">
+        <v>30.047944999999999</v>
+      </c>
+      <c r="T113">
+        <v>2.8421259999999999</v>
+      </c>
+      <c r="U113">
+        <v>181</v>
+      </c>
+      <c r="V113">
+        <v>3.5234570000000001</v>
+      </c>
+      <c r="W113">
+        <v>24.237569000000001</v>
+      </c>
+      <c r="X113">
+        <v>28</v>
+      </c>
+      <c r="Y113">
+        <v>156.67857100000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>25</v>
+      </c>
+      <c r="B114" t="s">
+        <v>26</v>
+      </c>
+      <c r="C114" t="s">
+        <v>186</v>
+      </c>
+      <c r="D114" t="s">
+        <v>87</v>
+      </c>
+      <c r="E114" t="s">
+        <v>29</v>
+      </c>
+      <c r="F114">
+        <v>91</v>
+      </c>
+      <c r="G114" t="s">
+        <v>39</v>
+      </c>
+      <c r="H114">
+        <v>2855</v>
+      </c>
+      <c r="I114">
+        <v>1.6273200000000001</v>
+      </c>
+      <c r="J114">
+        <v>48.560439559999999</v>
+      </c>
+      <c r="K114">
+        <v>160</v>
+      </c>
+      <c r="L114" t="s">
+        <v>30</v>
+      </c>
+      <c r="M114">
+        <v>4419</v>
+      </c>
+      <c r="N114" t="s">
+        <v>187</v>
+      </c>
+      <c r="O114">
+        <v>4646</v>
+      </c>
+      <c r="P114">
+        <v>951.14076599999999</v>
+      </c>
+      <c r="Q114">
+        <v>91</v>
+      </c>
+      <c r="S114">
+        <v>48.56044</v>
+      </c>
+      <c r="T114">
+        <v>1.958674</v>
+      </c>
+      <c r="U114">
+        <v>110</v>
+      </c>
+      <c r="V114">
+        <v>2.3676279999999998</v>
+      </c>
+      <c r="W114">
+        <v>40.172727000000002</v>
+      </c>
+      <c r="X114">
+        <v>80</v>
+      </c>
+      <c r="Y114">
+        <v>55.237499999999997</v>
+      </c>
+    </row>
+    <row r="115" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>25</v>
+      </c>
+      <c r="B115" t="s">
+        <v>26</v>
+      </c>
+      <c r="C115" t="s">
+        <v>188</v>
+      </c>
+      <c r="D115" t="s">
+        <v>28</v>
+      </c>
+      <c r="E115" t="s">
+        <v>29</v>
+      </c>
+      <c r="F115">
+        <v>87</v>
+      </c>
+      <c r="G115" t="s">
+        <v>39</v>
+      </c>
+      <c r="H115">
+        <v>2219</v>
+      </c>
+      <c r="I115">
+        <v>1.1631370000000001</v>
+      </c>
+      <c r="J115">
+        <v>50.505747130000003</v>
+      </c>
+      <c r="K115">
+        <v>160</v>
+      </c>
+      <c r="L115" t="s">
+        <v>30</v>
+      </c>
+      <c r="M115">
+        <v>4394</v>
+      </c>
+      <c r="N115" t="s">
+        <v>119</v>
+      </c>
+      <c r="O115">
+        <v>2581</v>
+      </c>
+      <c r="P115">
+        <v>1702.440914</v>
+      </c>
+      <c r="Q115">
+        <v>87</v>
+      </c>
+      <c r="S115">
+        <v>50.505747</v>
+      </c>
+      <c r="T115">
+        <v>3.370787</v>
+      </c>
+      <c r="U115">
+        <v>91</v>
+      </c>
+      <c r="V115">
+        <v>3.5257649999999998</v>
+      </c>
+      <c r="W115">
+        <v>48.285713999999999</v>
+      </c>
+      <c r="X115">
+        <v>55</v>
+      </c>
+      <c r="Y115">
+        <v>79.890908999999994</v>
+      </c>
+    </row>
+    <row r="116" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>25</v>
+      </c>
+      <c r="B116" t="s">
+        <v>26</v>
+      </c>
+      <c r="C116" t="s">
+        <v>189</v>
+      </c>
+      <c r="D116" t="s">
+        <v>38</v>
+      </c>
+      <c r="E116" t="s">
+        <v>29</v>
+      </c>
+      <c r="F116">
+        <v>179</v>
+      </c>
+      <c r="G116" t="s">
+        <v>39</v>
+      </c>
+      <c r="H116">
+        <v>3014</v>
+      </c>
+      <c r="I116">
+        <v>1.6877899999999999</v>
+      </c>
+      <c r="J116">
+        <v>24.564245809999999</v>
+      </c>
+      <c r="K116">
+        <v>160</v>
+      </c>
+      <c r="L116" t="s">
+        <v>30</v>
+      </c>
+      <c r="M116">
+        <v>4397</v>
+      </c>
+      <c r="N116" t="s">
+        <v>113</v>
+      </c>
+      <c r="O116">
+        <v>5087</v>
+      </c>
+      <c r="P116">
+        <v>864.36013400000002</v>
+      </c>
+      <c r="Q116">
+        <v>179</v>
+      </c>
+      <c r="S116">
+        <v>24.564246000000001</v>
+      </c>
+      <c r="T116">
+        <v>3.5187729999999999</v>
+      </c>
+      <c r="U116">
+        <v>221</v>
+      </c>
+      <c r="V116">
+        <v>4.3444070000000004</v>
+      </c>
+      <c r="W116">
+        <v>19.895928000000001</v>
+      </c>
+      <c r="X116">
+        <v>41</v>
+      </c>
+      <c r="Y116">
+        <v>107.24390200000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>25</v>
+      </c>
+      <c r="B117" t="s">
+        <v>26</v>
+      </c>
+      <c r="C117" t="s">
+        <v>190</v>
+      </c>
+      <c r="D117" t="s">
+        <v>38</v>
+      </c>
+      <c r="E117" t="s">
+        <v>29</v>
+      </c>
+      <c r="F117">
+        <v>260</v>
+      </c>
+      <c r="G117" t="s">
+        <v>39</v>
+      </c>
+      <c r="H117">
+        <v>3654</v>
+      </c>
+      <c r="I117">
+        <v>1.5377670000000001</v>
+      </c>
+      <c r="J117">
+        <v>16.926923080000002</v>
+      </c>
+      <c r="K117">
+        <v>160</v>
+      </c>
+      <c r="L117" t="s">
+        <v>30</v>
+      </c>
+      <c r="M117">
+        <v>4401</v>
+      </c>
+      <c r="N117" t="s">
+        <v>113</v>
+      </c>
+      <c r="O117">
+        <v>5619</v>
+      </c>
+      <c r="P117">
+        <v>783.23545100000001</v>
+      </c>
+      <c r="Q117">
+        <v>260</v>
+      </c>
+      <c r="S117">
+        <v>16.926922999999999</v>
+      </c>
+      <c r="T117">
+        <v>4.6271579999999997</v>
+      </c>
+      <c r="U117">
+        <v>291</v>
+      </c>
+      <c r="V117">
+        <v>5.1788569999999998</v>
+      </c>
+      <c r="W117">
+        <v>15.123711</v>
+      </c>
+      <c r="X117">
+        <v>244</v>
+      </c>
+      <c r="Y117">
+        <v>18.036885000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>25</v>
+      </c>
+      <c r="B118" t="s">
+        <v>26</v>
+      </c>
+      <c r="C118" t="s">
+        <v>191</v>
+      </c>
+      <c r="D118" t="s">
+        <v>38</v>
+      </c>
+      <c r="E118" t="s">
+        <v>29</v>
+      </c>
+      <c r="F118">
+        <v>109</v>
+      </c>
+      <c r="G118" t="s">
+        <v>39</v>
+      </c>
+      <c r="H118">
+        <v>3714</v>
+      </c>
+      <c r="I118">
+        <v>1.3123320000000001</v>
+      </c>
+      <c r="J118">
+        <v>40.458715599999998</v>
+      </c>
+      <c r="K118">
+        <v>160</v>
+      </c>
+      <c r="L118" t="s">
+        <v>30</v>
+      </c>
+      <c r="M118">
+        <v>4410</v>
+      </c>
+      <c r="N118" t="s">
+        <v>113</v>
+      </c>
+      <c r="O118">
+        <v>4874</v>
+      </c>
+      <c r="P118">
+        <v>904.80098499999997</v>
+      </c>
+      <c r="Q118">
+        <v>109</v>
+      </c>
+      <c r="S118">
+        <v>40.458716000000003</v>
+      </c>
+      <c r="T118">
+        <v>2.2363559999999998</v>
+      </c>
+      <c r="U118">
+        <v>119</v>
+      </c>
+      <c r="V118">
+        <v>2.4415260000000001</v>
+      </c>
+      <c r="W118">
+        <v>37.058824000000001</v>
+      </c>
+      <c r="X118">
+        <v>96</v>
+      </c>
+      <c r="Y118">
+        <v>45.9375</v>
+      </c>
+    </row>
+    <row r="119" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>25</v>
+      </c>
+      <c r="B119" t="s">
+        <v>26</v>
+      </c>
+      <c r="C119" t="s">
+        <v>192</v>
+      </c>
+      <c r="D119" t="s">
+        <v>38</v>
+      </c>
+      <c r="E119" t="s">
+        <v>29</v>
+      </c>
+      <c r="F119">
+        <v>271</v>
+      </c>
+      <c r="G119" t="s">
+        <v>39</v>
+      </c>
+      <c r="H119">
+        <v>3504</v>
+      </c>
+      <c r="I119">
+        <v>1.5351030000000001</v>
+      </c>
+      <c r="J119">
+        <v>16.243542439999999</v>
+      </c>
+      <c r="K119">
+        <v>160</v>
+      </c>
+      <c r="L119" t="s">
+        <v>30</v>
+      </c>
+      <c r="M119">
+        <v>4402</v>
+      </c>
+      <c r="N119" t="s">
+        <v>113</v>
+      </c>
+      <c r="O119">
+        <v>5379</v>
+      </c>
+      <c r="P119">
+        <v>818.36772599999995</v>
+      </c>
+      <c r="Q119">
+        <v>271</v>
+      </c>
+      <c r="S119">
+        <v>16.243542000000001</v>
+      </c>
+      <c r="T119">
+        <v>5.0381109999999998</v>
+      </c>
+      <c r="U119">
+        <v>301</v>
+      </c>
+      <c r="V119">
+        <v>5.5958360000000003</v>
+      </c>
+      <c r="W119">
+        <v>14.624585</v>
+      </c>
+      <c r="X119">
+        <v>12</v>
+      </c>
+      <c r="Y119">
+        <v>366.83333299999998</v>
+      </c>
+    </row>
+    <row r="120" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>25</v>
+      </c>
+      <c r="B120" t="s">
+        <v>26</v>
+      </c>
+      <c r="C120" t="s">
+        <v>193</v>
+      </c>
+      <c r="D120" t="s">
+        <v>38</v>
+      </c>
+      <c r="E120" t="s">
+        <v>29</v>
+      </c>
+      <c r="F120">
+        <v>200</v>
+      </c>
+      <c r="G120" t="s">
+        <v>39</v>
+      </c>
+      <c r="H120">
+        <v>3607</v>
+      </c>
+      <c r="I120">
+        <v>1.5001389999999999</v>
+      </c>
+      <c r="J120">
+        <v>22.07</v>
+      </c>
+      <c r="K120">
+        <v>160</v>
+      </c>
+      <c r="L120" t="s">
+        <v>30</v>
+      </c>
+      <c r="M120">
+        <v>4414</v>
+      </c>
+      <c r="N120" t="s">
+        <v>113</v>
+      </c>
+      <c r="O120">
+        <v>5411</v>
+      </c>
+      <c r="P120">
+        <v>815.74570300000005</v>
+      </c>
+      <c r="Q120">
+        <v>200</v>
+      </c>
+      <c r="S120">
+        <v>22.07</v>
+      </c>
+      <c r="T120">
+        <v>3.6961740000000001</v>
+      </c>
+      <c r="U120">
+        <v>236</v>
+      </c>
+      <c r="V120">
+        <v>4.3614860000000002</v>
+      </c>
+      <c r="W120">
+        <v>18.703389999999999</v>
+      </c>
+      <c r="X120">
+        <v>188</v>
+      </c>
+      <c r="Y120">
+        <v>23.478722999999999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>25</v>
+      </c>
+      <c r="B121" t="s">
+        <v>26</v>
+      </c>
+      <c r="C121" t="s">
+        <v>194</v>
+      </c>
+      <c r="D121" t="s">
+        <v>38</v>
+      </c>
+      <c r="E121" t="s">
+        <v>29</v>
+      </c>
+      <c r="F121">
+        <v>183</v>
+      </c>
+      <c r="G121" t="s">
+        <v>39</v>
+      </c>
+      <c r="H121">
+        <v>4203</v>
+      </c>
+      <c r="I121">
+        <v>1.530573</v>
+      </c>
+      <c r="J121">
+        <v>24.038251370000001</v>
+      </c>
+      <c r="K121">
+        <v>160</v>
+      </c>
+      <c r="L121" t="s">
+        <v>30</v>
+      </c>
+      <c r="M121">
+        <v>4399</v>
+      </c>
+      <c r="N121" t="s">
+        <v>113</v>
+      </c>
+      <c r="O121">
+        <v>6433</v>
+      </c>
+      <c r="P121">
+        <v>683.817814</v>
+      </c>
+      <c r="Q121">
+        <v>183</v>
+      </c>
+      <c r="S121">
+        <v>24.038250999999999</v>
+      </c>
+      <c r="T121">
+        <v>2.8447070000000001</v>
+      </c>
+      <c r="U121">
+        <v>246</v>
+      </c>
+      <c r="V121">
+        <v>3.8240319999999999</v>
+      </c>
+      <c r="W121">
+        <v>17.882114000000001</v>
+      </c>
+      <c r="X121">
+        <v>19</v>
+      </c>
+      <c r="Y121">
+        <v>231.52631600000001</v>
+      </c>
+    </row>
+    <row r="122" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>25</v>
+      </c>
+      <c r="B122" t="s">
+        <v>26</v>
+      </c>
+      <c r="C122" t="s">
+        <v>195</v>
+      </c>
+      <c r="D122" t="s">
+        <v>38</v>
+      </c>
+      <c r="E122" t="s">
+        <v>29</v>
+      </c>
+      <c r="F122">
+        <v>145</v>
+      </c>
+      <c r="G122" t="s">
+        <v>39</v>
+      </c>
+      <c r="H122">
+        <v>3648</v>
+      </c>
+      <c r="I122">
+        <v>1.3983000000000001</v>
+      </c>
+      <c r="J122">
+        <v>30.406896549999999</v>
+      </c>
+      <c r="K122">
+        <v>160</v>
+      </c>
+      <c r="L122" t="s">
+        <v>30</v>
+      </c>
+      <c r="M122">
+        <v>4409</v>
+      </c>
+      <c r="N122" t="s">
+        <v>113</v>
+      </c>
+      <c r="O122">
+        <v>5101</v>
+      </c>
+      <c r="P122">
+        <v>864.34032500000001</v>
+      </c>
+      <c r="Q122">
+        <v>145</v>
+      </c>
+      <c r="S122">
+        <v>30.406897000000001</v>
+      </c>
+      <c r="T122">
+        <v>2.8425799999999999</v>
+      </c>
+      <c r="U122">
+        <v>185</v>
+      </c>
+      <c r="V122">
+        <v>3.6267399999999999</v>
+      </c>
+      <c r="W122">
+        <v>23.832432000000001</v>
+      </c>
+      <c r="X122">
+        <v>152</v>
+      </c>
+      <c r="Y122">
+        <v>29.006578999999999</v>
+      </c>
+    </row>
+    <row r="123" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>25</v>
+      </c>
+      <c r="B123" t="s">
+        <v>26</v>
+      </c>
+      <c r="C123" t="s">
+        <v>196</v>
+      </c>
+      <c r="D123" t="s">
+        <v>38</v>
+      </c>
+      <c r="E123" t="s">
+        <v>29</v>
+      </c>
+      <c r="F123">
+        <v>107</v>
+      </c>
+      <c r="G123" t="s">
+        <v>39</v>
+      </c>
+      <c r="H123">
+        <v>2350</v>
+      </c>
+      <c r="I123">
+        <v>1.621702</v>
+      </c>
+      <c r="J123">
+        <v>41.261682239999999</v>
+      </c>
+      <c r="K123">
+        <v>160</v>
+      </c>
+      <c r="L123" t="s">
+        <v>30</v>
+      </c>
+      <c r="M123">
+        <v>4415</v>
+      </c>
+      <c r="N123" t="s">
+        <v>113</v>
+      </c>
+      <c r="O123">
+        <v>3811</v>
+      </c>
+      <c r="P123">
+        <v>1158.4885859999999</v>
+      </c>
+      <c r="Q123">
+        <v>107</v>
+      </c>
+      <c r="S123">
+        <v>41.261682</v>
+      </c>
+      <c r="T123">
+        <v>2.8076620000000001</v>
+      </c>
+      <c r="U123">
+        <v>131</v>
+      </c>
+      <c r="V123">
+        <v>3.4374180000000001</v>
+      </c>
+      <c r="W123">
+        <v>33.702289999999998</v>
+      </c>
+      <c r="X123">
+        <v>93</v>
+      </c>
+      <c r="Y123">
+        <v>47.473117999999999</v>
+      </c>
+    </row>
+    <row r="124" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>25</v>
+      </c>
+      <c r="B124" t="s">
+        <v>26</v>
+      </c>
+      <c r="C124" t="s">
+        <v>197</v>
+      </c>
+      <c r="D124" t="s">
+        <v>38</v>
+      </c>
+      <c r="E124" t="s">
+        <v>29</v>
+      </c>
+      <c r="F124">
+        <v>62</v>
+      </c>
+      <c r="G124" t="s">
+        <v>39</v>
+      </c>
+      <c r="H124">
+        <v>3982</v>
+      </c>
+      <c r="I124">
+        <v>1.693872</v>
+      </c>
+      <c r="J124">
+        <v>70.919354839999997</v>
+      </c>
+      <c r="K124">
+        <v>160</v>
+      </c>
+      <c r="L124" t="s">
+        <v>30</v>
+      </c>
+      <c r="M124">
+        <v>4397</v>
+      </c>
+      <c r="N124" t="s">
+        <v>113</v>
+      </c>
+      <c r="O124">
+        <v>6745</v>
+      </c>
+      <c r="P124">
+        <v>651.89028900000005</v>
+      </c>
+      <c r="Q124">
+        <v>62</v>
+      </c>
+      <c r="S124">
+        <v>70.919354999999996</v>
+      </c>
+      <c r="T124">
+        <v>0.91919899999999999</v>
+      </c>
+      <c r="U124">
+        <v>70</v>
+      </c>
+      <c r="V124">
+        <v>1.037806</v>
+      </c>
+      <c r="W124">
+        <v>62.814286000000003</v>
+      </c>
+      <c r="X124">
+        <v>50</v>
+      </c>
+      <c r="Y124">
+        <v>87.94</v>
+      </c>
+    </row>
+    <row r="125" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>25</v>
+      </c>
+      <c r="B125" t="s">
+        <v>26</v>
+      </c>
+      <c r="C125" t="s">
+        <v>198</v>
+      </c>
+      <c r="D125" t="s">
+        <v>38</v>
+      </c>
+      <c r="E125" t="s">
+        <v>29</v>
+      </c>
+      <c r="F125">
+        <v>257</v>
+      </c>
+      <c r="G125" t="s">
+        <v>39</v>
+      </c>
+      <c r="H125">
+        <v>4150</v>
+      </c>
+      <c r="I125">
+        <v>1.3746989999999999</v>
+      </c>
+      <c r="J125">
+        <v>17.073929960000001</v>
+      </c>
+      <c r="K125">
+        <v>160</v>
+      </c>
+      <c r="L125" t="s">
+        <v>30</v>
+      </c>
+      <c r="M125">
+        <v>4388</v>
+      </c>
+      <c r="N125" t="s">
+        <v>113</v>
+      </c>
+      <c r="O125">
+        <v>5705</v>
+      </c>
+      <c r="P125">
+        <v>769.14986899999997</v>
+      </c>
+      <c r="Q125">
+        <v>257</v>
+      </c>
+      <c r="S125">
+        <v>17.073930000000001</v>
+      </c>
+      <c r="T125">
+        <v>4.5048199999999996</v>
+      </c>
+      <c r="U125">
+        <v>317</v>
+      </c>
+      <c r="V125">
+        <v>5.5565290000000003</v>
+      </c>
+      <c r="W125">
+        <v>13.842271</v>
+      </c>
+      <c r="X125">
+        <v>229</v>
+      </c>
+      <c r="Y125">
+        <v>19.161572</v>
+      </c>
+    </row>
+    <row r="126" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>25</v>
+      </c>
+      <c r="B126" t="s">
+        <v>26</v>
+      </c>
+      <c r="C126" t="s">
+        <v>199</v>
+      </c>
+      <c r="D126" t="s">
+        <v>38</v>
+      </c>
+      <c r="E126" t="s">
+        <v>29</v>
+      </c>
+      <c r="F126">
+        <v>180</v>
+      </c>
+      <c r="G126" t="s">
+        <v>39</v>
+      </c>
+      <c r="H126">
+        <v>5547</v>
+      </c>
+      <c r="I126">
+        <v>1.385974</v>
+      </c>
+      <c r="J126">
+        <v>24.466666669999999</v>
+      </c>
+      <c r="K126">
+        <v>160</v>
+      </c>
+      <c r="L126" t="s">
+        <v>30</v>
+      </c>
+      <c r="M126">
+        <v>4404</v>
+      </c>
+      <c r="N126" t="s">
+        <v>113</v>
+      </c>
+      <c r="O126">
+        <v>7688</v>
+      </c>
+      <c r="P126">
+        <v>572.84079099999997</v>
+      </c>
+      <c r="Q126">
+        <v>180</v>
+      </c>
+      <c r="S126">
+        <v>24.466667000000001</v>
+      </c>
+      <c r="T126">
+        <v>2.3413110000000001</v>
+      </c>
+      <c r="U126">
+        <v>271</v>
+      </c>
+      <c r="V126">
+        <v>3.5249739999999998</v>
+      </c>
+      <c r="W126">
+        <v>16.250923</v>
+      </c>
+      <c r="X126">
+        <v>195</v>
+      </c>
+      <c r="Y126">
+        <v>22.584614999999999</v>
+      </c>
+    </row>
+    <row r="127" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>25</v>
+      </c>
+      <c r="B127" t="s">
+        <v>26</v>
+      </c>
+      <c r="C127" t="s">
+        <v>200</v>
+      </c>
+      <c r="D127" t="s">
+        <v>38</v>
+      </c>
+      <c r="E127" t="s">
+        <v>29</v>
+      </c>
+      <c r="F127">
+        <v>328</v>
+      </c>
+      <c r="G127" t="s">
+        <v>39</v>
+      </c>
+      <c r="H127">
+        <v>4127</v>
+      </c>
+      <c r="I127">
+        <v>1.3271139999999999</v>
+      </c>
+      <c r="J127">
+        <v>13.3445122</v>
+      </c>
+      <c r="K127">
+        <v>160</v>
+      </c>
+      <c r="L127" t="s">
+        <v>30</v>
+      </c>
+      <c r="M127">
+        <v>4377</v>
+      </c>
+      <c r="N127" t="s">
+        <v>113</v>
+      </c>
+      <c r="O127">
+        <v>5477</v>
+      </c>
+      <c r="P127">
+        <v>799.160124</v>
+      </c>
+      <c r="Q127">
+        <v>328</v>
+      </c>
+      <c r="S127">
+        <v>13.344512</v>
+      </c>
+      <c r="T127">
+        <v>5.9886799999999996</v>
+      </c>
+      <c r="U127">
+        <v>378</v>
+      </c>
+      <c r="V127">
+        <v>6.9015880000000003</v>
+      </c>
+      <c r="W127">
+        <v>11.579364999999999</v>
+      </c>
+      <c r="X127">
+        <v>298</v>
+      </c>
+      <c r="Y127">
+        <v>14.687919000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>25</v>
+      </c>
+      <c r="B128" t="s">
+        <v>26</v>
+      </c>
+      <c r="C128" t="s">
+        <v>201</v>
+      </c>
+      <c r="D128" t="s">
+        <v>38</v>
+      </c>
+      <c r="E128" t="s">
+        <v>29</v>
+      </c>
+      <c r="F128">
+        <v>536</v>
+      </c>
+      <c r="G128" t="s">
+        <v>39</v>
+      </c>
+      <c r="H128">
+        <v>4514</v>
+      </c>
+      <c r="I128">
+        <v>1.385246</v>
+      </c>
+      <c r="J128">
+        <v>8.1958955200000005</v>
+      </c>
+      <c r="K128">
+        <v>160</v>
+      </c>
+      <c r="L128" t="s">
+        <v>30</v>
+      </c>
+      <c r="M128">
+        <v>4393</v>
+      </c>
+      <c r="N128" t="s">
+        <v>113</v>
+      </c>
+      <c r="O128">
+        <v>6253</v>
+      </c>
+      <c r="P128">
+        <v>702.542779</v>
+      </c>
+      <c r="Q128">
+        <v>536</v>
+      </c>
+      <c r="S128">
+        <v>8.1958959999999994</v>
+      </c>
+      <c r="T128">
+        <v>8.571885</v>
+      </c>
+      <c r="U128">
+        <v>635</v>
+      </c>
+      <c r="V128">
+        <v>10.155125999999999</v>
+      </c>
+      <c r="W128">
+        <v>6.9181100000000004</v>
+      </c>
+      <c r="X128">
+        <v>518</v>
+      </c>
+      <c r="Y128">
+        <v>8.4806950000000008</v>
+      </c>
+    </row>
+    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>25</v>
+      </c>
+      <c r="B129" t="s">
+        <v>26</v>
+      </c>
+      <c r="C129" t="s">
+        <v>202</v>
+      </c>
+      <c r="D129" t="s">
+        <v>38</v>
+      </c>
+      <c r="E129" t="s">
+        <v>29</v>
+      </c>
+      <c r="F129">
+        <v>605</v>
+      </c>
+      <c r="G129" t="s">
+        <v>39</v>
+      </c>
+      <c r="H129">
+        <v>5895</v>
+      </c>
+      <c r="I129">
+        <v>1.37201</v>
+      </c>
+      <c r="J129">
+        <v>7.2644628100000004</v>
+      </c>
+      <c r="K129">
+        <v>160</v>
+      </c>
+      <c r="L129" t="s">
+        <v>30</v>
+      </c>
+      <c r="M129">
+        <v>4395</v>
+      </c>
+      <c r="N129" t="s">
+        <v>113</v>
+      </c>
+      <c r="O129">
+        <v>8088</v>
+      </c>
+      <c r="P129">
+        <v>543.39762599999995</v>
+      </c>
+      <c r="Q129">
+        <v>605</v>
+      </c>
+      <c r="S129">
+        <v>7.2644630000000001</v>
+      </c>
+      <c r="T129">
+        <v>7.4802179999999998</v>
+      </c>
+      <c r="U129">
+        <v>738</v>
+      </c>
+      <c r="V129">
+        <v>9.1246290000000005</v>
+      </c>
+      <c r="W129">
+        <v>5.9552849999999999</v>
+      </c>
+      <c r="X129">
+        <v>575</v>
+      </c>
+      <c r="Y129">
+        <v>7.643478</v>
+      </c>
+    </row>
+    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>25</v>
+      </c>
+      <c r="B130" t="s">
+        <v>26</v>
+      </c>
+      <c r="C130" t="s">
+        <v>203</v>
+      </c>
+      <c r="D130" t="s">
+        <v>38</v>
+      </c>
+      <c r="E130" t="s">
+        <v>29</v>
+      </c>
+      <c r="F130">
+        <v>284</v>
+      </c>
+      <c r="G130" t="s">
+        <v>39</v>
+      </c>
+      <c r="H130">
+        <v>4724</v>
+      </c>
+      <c r="I130">
+        <v>1.3738360000000001</v>
+      </c>
+      <c r="J130">
+        <v>15.52112676</v>
+      </c>
+      <c r="K130">
+        <v>160</v>
+      </c>
+      <c r="L130" t="s">
+        <v>30</v>
+      </c>
+      <c r="M130">
+        <v>4408</v>
+      </c>
+      <c r="N130" t="s">
+        <v>113</v>
+      </c>
+      <c r="O130">
+        <v>6490</v>
+      </c>
+      <c r="P130">
+        <v>679.19876699999998</v>
+      </c>
+      <c r="Q130">
+        <v>284</v>
+      </c>
+      <c r="S130">
+        <v>15.521127</v>
+      </c>
+      <c r="T130">
+        <v>4.3759629999999996</v>
+      </c>
+      <c r="U130">
+        <v>352</v>
+      </c>
+      <c r="V130">
+        <v>5.4237289999999998</v>
+      </c>
+      <c r="W130">
+        <v>12.522727</v>
+      </c>
+      <c r="X130">
+        <v>262</v>
+      </c>
+      <c r="Y130">
+        <v>16.824427</v>
+      </c>
+    </row>
+    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>25</v>
+      </c>
+      <c r="B131" t="s">
+        <v>26</v>
+      </c>
+      <c r="C131" t="s">
+        <v>204</v>
+      </c>
+      <c r="D131" t="s">
+        <v>38</v>
+      </c>
+      <c r="E131" t="s">
+        <v>29</v>
+      </c>
+      <c r="F131">
+        <v>251</v>
+      </c>
+      <c r="G131" t="s">
+        <v>39</v>
+      </c>
+      <c r="H131">
+        <v>3900</v>
+      </c>
+      <c r="I131">
+        <v>1.463846</v>
+      </c>
+      <c r="J131">
+        <v>17.545816729999999</v>
+      </c>
+      <c r="K131">
+        <v>160</v>
+      </c>
+      <c r="L131" t="s">
+        <v>30</v>
+      </c>
+      <c r="M131">
+        <v>4404</v>
+      </c>
+      <c r="N131" t="s">
+        <v>113</v>
+      </c>
+      <c r="O131">
+        <v>5709</v>
+      </c>
+      <c r="P131">
+        <v>771.41355799999997</v>
+      </c>
+      <c r="Q131">
+        <v>251</v>
+      </c>
+      <c r="S131">
+        <v>17.545817</v>
+      </c>
+      <c r="T131">
+        <v>4.3965670000000001</v>
+      </c>
+      <c r="U131">
+        <v>304</v>
+      </c>
+      <c r="V131">
+        <v>5.3249259999999996</v>
+      </c>
+      <c r="W131">
+        <v>14.486841999999999</v>
+      </c>
+      <c r="X131">
+        <v>244</v>
+      </c>
+      <c r="Y131">
+        <v>18.04918</v>
+      </c>
+    </row>
+    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>25</v>
+      </c>
+      <c r="B132" t="s">
+        <v>26</v>
+      </c>
+      <c r="C132" t="s">
+        <v>205</v>
+      </c>
+      <c r="D132" t="s">
+        <v>38</v>
+      </c>
+      <c r="E132" t="s">
+        <v>29</v>
+      </c>
+      <c r="F132">
+        <v>205</v>
+      </c>
+      <c r="G132" t="s">
+        <v>39</v>
+      </c>
+      <c r="H132">
+        <v>4704</v>
+      </c>
+      <c r="I132">
+        <v>1.275085</v>
+      </c>
+      <c r="J132">
+        <v>21.56097561</v>
+      </c>
+      <c r="K132">
+        <v>160</v>
+      </c>
+      <c r="L132" t="s">
+        <v>30</v>
+      </c>
+      <c r="M132">
+        <v>4420</v>
+      </c>
+      <c r="N132" t="s">
+        <v>113</v>
+      </c>
+      <c r="O132">
+        <v>5998</v>
+      </c>
+      <c r="P132">
+        <v>736.91230399999995</v>
+      </c>
+      <c r="Q132">
+        <v>205</v>
+      </c>
+      <c r="S132">
+        <v>21.560976</v>
+      </c>
+      <c r="T132">
+        <v>3.4178060000000001</v>
+      </c>
+      <c r="U132">
+        <v>258</v>
+      </c>
+      <c r="V132">
+        <v>4.3014340000000004</v>
+      </c>
+      <c r="W132">
+        <v>17.131782999999999</v>
+      </c>
+      <c r="X132">
+        <v>202</v>
+      </c>
+      <c r="Y132">
+        <v>21.881188000000002</v>
+      </c>
+    </row>
+    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>25</v>
+      </c>
+      <c r="B133" t="s">
+        <v>26</v>
+      </c>
+      <c r="C133" t="s">
+        <v>206</v>
+      </c>
+      <c r="D133" t="s">
+        <v>38</v>
+      </c>
+      <c r="E133" t="s">
+        <v>29</v>
+      </c>
+      <c r="F133">
+        <v>76</v>
+      </c>
+      <c r="G133" t="s">
+        <v>39</v>
+      </c>
+      <c r="H133">
+        <v>3455</v>
+      </c>
+      <c r="I133">
+        <v>1.6824889999999999</v>
+      </c>
+      <c r="J133">
+        <v>58</v>
+      </c>
+      <c r="K133">
+        <v>160</v>
+      </c>
+      <c r="L133" t="s">
+        <v>30</v>
+      </c>
+      <c r="M133">
+        <v>4408</v>
+      </c>
+      <c r="N133" t="s">
+        <v>113</v>
+      </c>
+      <c r="O133">
+        <v>5813</v>
+      </c>
+      <c r="P133">
+        <v>758.30036099999995</v>
+      </c>
+      <c r="Q133">
+        <v>76</v>
+      </c>
+      <c r="S133">
+        <v>58</v>
+      </c>
+      <c r="T133">
+        <v>1.3074140000000001</v>
+      </c>
+      <c r="U133">
+        <v>95</v>
+      </c>
+      <c r="V133">
+        <v>1.6342680000000001</v>
+      </c>
+      <c r="W133">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>25</v>
+      </c>
+      <c r="B134" t="s">
+        <v>26</v>
+      </c>
+      <c r="C134" t="s">
+        <v>207</v>
+      </c>
+      <c r="D134" t="s">
+        <v>38</v>
+      </c>
+      <c r="E134" t="s">
+        <v>29</v>
+      </c>
+      <c r="F134">
+        <v>167</v>
+      </c>
+      <c r="G134" t="s">
+        <v>39</v>
+      </c>
+      <c r="H134">
+        <v>3648</v>
+      </c>
+      <c r="I134">
+        <v>1.233279</v>
+      </c>
+      <c r="J134">
+        <v>26.419161679999998</v>
+      </c>
+      <c r="K134">
+        <v>160</v>
+      </c>
+      <c r="L134" t="s">
+        <v>30</v>
+      </c>
+      <c r="M134">
+        <v>4412</v>
+      </c>
+      <c r="N134" t="s">
+        <v>113</v>
+      </c>
+      <c r="O134">
+        <v>4499</v>
+      </c>
+      <c r="P134">
+        <v>980.66236900000001</v>
+      </c>
+      <c r="Q134">
+        <v>167</v>
+      </c>
+      <c r="S134">
+        <v>26.419162</v>
+      </c>
+      <c r="T134">
+        <v>3.7119360000000001</v>
+      </c>
+      <c r="U134">
+        <v>182</v>
+      </c>
+      <c r="V134">
+        <v>4.0453429999999999</v>
+      </c>
+      <c r="W134">
+        <v>24.241758000000001</v>
+      </c>
+      <c r="X134">
+        <v>139</v>
+      </c>
+      <c r="Y134">
+        <v>31.741007</v>
+      </c>
+    </row>
+    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>25</v>
+      </c>
+      <c r="B135" t="s">
+        <v>26</v>
+      </c>
+      <c r="C135" t="s">
+        <v>208</v>
+      </c>
+      <c r="D135" t="s">
+        <v>38</v>
+      </c>
+      <c r="E135" t="s">
+        <v>29</v>
+      </c>
+      <c r="F135">
+        <v>199</v>
+      </c>
+      <c r="G135" t="s">
+        <v>39</v>
+      </c>
+      <c r="H135">
+        <v>5675</v>
+      </c>
+      <c r="I135">
+        <v>1.1559470000000001</v>
+      </c>
+      <c r="J135">
+        <v>21.86934673</v>
+      </c>
+      <c r="K135">
+        <v>160</v>
+      </c>
+      <c r="L135" t="s">
+        <v>30</v>
+      </c>
+      <c r="M135">
+        <v>4352</v>
+      </c>
+      <c r="N135" t="s">
+        <v>113</v>
+      </c>
+      <c r="O135">
+        <v>6560</v>
+      </c>
+      <c r="P135">
+        <v>663.41463399999998</v>
+      </c>
+      <c r="Q135">
+        <v>199</v>
+      </c>
+      <c r="S135">
+        <v>21.869347000000001</v>
+      </c>
+      <c r="T135">
+        <v>3.0335369999999999</v>
+      </c>
+      <c r="U135">
+        <v>230</v>
+      </c>
+      <c r="V135">
+        <v>3.5060980000000002</v>
+      </c>
+      <c r="W135">
+        <v>18.921738999999999</v>
+      </c>
+      <c r="X135">
+        <v>195</v>
+      </c>
+      <c r="Y135">
+        <v>22.317948999999999</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>25</v>
+      </c>
+      <c r="B136" t="s">
+        <v>26</v>
+      </c>
+      <c r="C136" t="s">
+        <v>209</v>
+      </c>
+      <c r="D136" t="s">
+        <v>38</v>
+      </c>
+      <c r="E136" t="s">
+        <v>29</v>
+      </c>
+      <c r="F136">
+        <v>218</v>
+      </c>
+      <c r="G136" t="s">
+        <v>39</v>
+      </c>
+      <c r="H136">
+        <v>2504</v>
+      </c>
+      <c r="I136">
+        <v>1.3362620000000001</v>
+      </c>
+      <c r="J136">
+        <v>20.206422020000002</v>
+      </c>
+      <c r="K136">
+        <v>160</v>
+      </c>
+      <c r="L136" t="s">
+        <v>30</v>
+      </c>
+      <c r="M136">
+        <v>4405</v>
+      </c>
+      <c r="N136" t="s">
+        <v>113</v>
+      </c>
+      <c r="O136">
+        <v>3346</v>
+      </c>
+      <c r="P136">
+        <v>1316.49731</v>
+      </c>
+      <c r="Q136">
+        <v>218</v>
+      </c>
+      <c r="S136">
+        <v>20.206422</v>
+      </c>
+      <c r="T136">
+        <v>6.5152419999999998</v>
+      </c>
+      <c r="U136">
+        <v>230</v>
+      </c>
+      <c r="V136">
+        <v>6.8738789999999996</v>
+      </c>
+      <c r="W136">
+        <v>19.152173999999999</v>
+      </c>
+      <c r="X136">
+        <v>17</v>
+      </c>
+      <c r="Y136">
+        <v>259.11764699999998</v>
+      </c>
+    </row>
+    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>25</v>
+      </c>
+      <c r="B137" t="s">
+        <v>26</v>
+      </c>
+      <c r="C137" t="s">
+        <v>210</v>
+      </c>
+      <c r="D137" t="s">
+        <v>38</v>
+      </c>
+      <c r="E137" t="s">
+        <v>29</v>
+      </c>
+      <c r="F137">
+        <v>238</v>
+      </c>
+      <c r="G137" t="s">
+        <v>39</v>
+      </c>
+      <c r="H137">
+        <v>5837</v>
+      </c>
+      <c r="I137">
+        <v>1.1877679999999999</v>
+      </c>
+      <c r="J137">
+        <v>18.453781509999999</v>
+      </c>
+      <c r="K137">
+        <v>160</v>
+      </c>
+      <c r="L137" t="s">
+        <v>30</v>
+      </c>
+      <c r="M137">
+        <v>4392</v>
+      </c>
+      <c r="N137" t="s">
+        <v>113</v>
+      </c>
+      <c r="O137">
+        <v>6933</v>
+      </c>
+      <c r="P137">
+        <v>633.49199499999997</v>
+      </c>
+      <c r="Q137">
+        <v>238</v>
+      </c>
+      <c r="S137">
+        <v>18.453782</v>
+      </c>
+      <c r="T137">
+        <v>3.4328569999999998</v>
+      </c>
+      <c r="U137">
+        <v>286</v>
+      </c>
+      <c r="V137">
+        <v>4.1251980000000001</v>
+      </c>
+      <c r="W137">
+        <v>15.356643</v>
+      </c>
+      <c r="X137">
+        <v>227</v>
+      </c>
+      <c r="Y137">
+        <v>19.348018</v>
+      </c>
+    </row>
+    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>25</v>
+      </c>
+      <c r="B138" t="s">
+        <v>26</v>
+      </c>
+      <c r="C138" t="s">
+        <v>188</v>
+      </c>
+      <c r="D138" t="s">
+        <v>28</v>
+      </c>
+      <c r="E138" t="s">
+        <v>29</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>160</v>
+      </c>
+      <c r="L138" t="s">
+        <v>30</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138" t="s">
+        <v>119</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+      <c r="U138">
+        <v>0</v>
+      </c>
+      <c r="V138">
+        <v>0</v>
+      </c>
+      <c r="W138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>25</v>
+      </c>
+      <c r="B139" t="s">
+        <v>26</v>
+      </c>
+      <c r="C139" t="s">
+        <v>211</v>
+      </c>
+      <c r="D139" t="s">
+        <v>38</v>
+      </c>
+      <c r="E139" t="s">
+        <v>29</v>
+      </c>
+      <c r="F139">
+        <v>390</v>
+      </c>
+      <c r="G139" t="s">
+        <v>39</v>
+      </c>
+      <c r="H139">
+        <v>7705</v>
+      </c>
+      <c r="I139">
+        <v>1.2404930000000001</v>
+      </c>
+      <c r="J139">
+        <v>11.320512819999999</v>
+      </c>
+      <c r="K139">
+        <v>160</v>
+      </c>
+      <c r="L139" t="s">
+        <v>30</v>
+      </c>
+      <c r="M139">
+        <v>4415</v>
+      </c>
+      <c r="N139" t="s">
+        <v>113</v>
+      </c>
+      <c r="O139">
+        <v>9558</v>
+      </c>
+      <c r="P139">
+        <v>461.916719</v>
+      </c>
+      <c r="Q139">
+        <v>390</v>
+      </c>
+      <c r="S139">
+        <v>11.320513</v>
+      </c>
+      <c r="T139">
+        <v>4.0803520000000004</v>
+      </c>
+      <c r="U139">
+        <v>462</v>
+      </c>
+      <c r="V139">
+        <v>4.833647</v>
+      </c>
+      <c r="W139">
+        <v>9.5562769999999997</v>
+      </c>
+      <c r="X139">
+        <v>409</v>
+      </c>
+      <c r="Y139">
+        <v>10.794620999999999</v>
+      </c>
+    </row>
+    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>25</v>
+      </c>
+      <c r="B140" t="s">
+        <v>26</v>
+      </c>
+      <c r="C140" t="s">
+        <v>212</v>
+      </c>
+      <c r="D140" t="s">
+        <v>38</v>
+      </c>
+      <c r="E140" t="s">
+        <v>29</v>
+      </c>
+      <c r="F140">
+        <v>243</v>
+      </c>
+      <c r="G140" t="s">
+        <v>39</v>
+      </c>
+      <c r="H140">
+        <v>7179</v>
+      </c>
+      <c r="I140">
+        <v>1.2440450000000001</v>
+      </c>
+      <c r="J140">
+        <v>18.131687240000002</v>
+      </c>
+      <c r="K140">
+        <v>160</v>
+      </c>
+      <c r="L140" t="s">
+        <v>30</v>
+      </c>
+      <c r="M140">
+        <v>4406</v>
+      </c>
+      <c r="N140" t="s">
+        <v>113</v>
+      </c>
+      <c r="O140">
+        <v>8931</v>
+      </c>
+      <c r="P140">
+        <v>493.33781199999999</v>
+      </c>
+      <c r="Q140">
+        <v>243</v>
+      </c>
+      <c r="S140">
+        <v>18.131686999999999</v>
+      </c>
+      <c r="T140">
+        <v>2.7208600000000001</v>
+      </c>
+      <c r="U140">
+        <v>310</v>
+      </c>
+      <c r="V140">
+        <v>3.4710559999999999</v>
+      </c>
+      <c r="W140">
+        <v>14.212903000000001</v>
+      </c>
+      <c r="X140">
+        <v>289</v>
+      </c>
+      <c r="Y140">
+        <v>15.245675</v>
+      </c>
+    </row>
+    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>25</v>
+      </c>
+      <c r="B141" t="s">
+        <v>26</v>
+      </c>
+      <c r="C141" t="s">
+        <v>213</v>
+      </c>
+      <c r="D141" t="s">
+        <v>38</v>
+      </c>
+      <c r="E141" t="s">
+        <v>29</v>
+      </c>
+      <c r="F141">
+        <v>92</v>
+      </c>
+      <c r="G141" t="s">
+        <v>39</v>
+      </c>
+      <c r="H141">
+        <v>2363</v>
+      </c>
+      <c r="I141">
+        <v>1.1895899999999999</v>
+      </c>
+      <c r="J141">
+        <v>47.75</v>
+      </c>
+      <c r="K141">
+        <v>160</v>
+      </c>
+      <c r="L141" t="s">
+        <v>30</v>
+      </c>
+      <c r="M141">
+        <v>4393</v>
+      </c>
+      <c r="N141" t="s">
+        <v>63</v>
+      </c>
+      <c r="O141">
+        <v>2811</v>
+      </c>
+      <c r="P141">
+        <v>1562.789043</v>
+      </c>
+      <c r="Q141">
+        <v>92</v>
+      </c>
+      <c r="S141">
+        <v>47.75</v>
+      </c>
+      <c r="T141">
+        <v>3.2728570000000001</v>
+      </c>
+      <c r="U141">
+        <v>105</v>
+      </c>
+      <c r="V141">
+        <v>3.7353260000000001</v>
+      </c>
+      <c r="W141">
+        <v>41.838095000000003</v>
+      </c>
+      <c r="X141">
+        <v>79</v>
+      </c>
+      <c r="Y141">
+        <v>55.607595000000003</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>25</v>
+      </c>
+      <c r="B142" t="s">
+        <v>26</v>
+      </c>
+      <c r="C142" t="s">
+        <v>214</v>
+      </c>
+      <c r="D142" t="s">
+        <v>38</v>
+      </c>
+      <c r="E142" t="s">
+        <v>29</v>
+      </c>
+      <c r="F142">
+        <v>55</v>
+      </c>
+      <c r="G142" t="s">
+        <v>39</v>
+      </c>
+      <c r="H142">
+        <v>3499</v>
+      </c>
+      <c r="I142">
+        <v>1.178337</v>
+      </c>
+      <c r="J142">
+        <v>80.018181819999995</v>
+      </c>
+      <c r="K142">
+        <v>160</v>
+      </c>
+      <c r="L142" t="s">
+        <v>30</v>
+      </c>
+      <c r="M142">
+        <v>4401</v>
+      </c>
+      <c r="N142" t="s">
+        <v>63</v>
+      </c>
+      <c r="O142">
+        <v>4123</v>
+      </c>
+      <c r="P142">
+        <v>1067.426631</v>
+      </c>
+      <c r="Q142">
+        <v>55</v>
+      </c>
+      <c r="S142">
+        <v>80.018181999999996</v>
+      </c>
+      <c r="T142">
+        <v>1.3339799999999999</v>
+      </c>
+      <c r="U142">
+        <v>59</v>
+      </c>
+      <c r="V142">
+        <v>1.4309970000000001</v>
+      </c>
+      <c r="W142">
+        <v>74.593220000000002</v>
+      </c>
+      <c r="X142">
+        <v>39</v>
+      </c>
+      <c r="Y142">
+        <v>112.846154</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>25</v>
+      </c>
+      <c r="B143" t="s">
+        <v>26</v>
+      </c>
+      <c r="C143" t="s">
+        <v>215</v>
+      </c>
+      <c r="D143" t="s">
+        <v>38</v>
+      </c>
+      <c r="E143" t="s">
+        <v>29</v>
+      </c>
+      <c r="F143">
+        <v>105</v>
+      </c>
+      <c r="G143" t="s">
+        <v>39</v>
+      </c>
+      <c r="H143">
+        <v>3131</v>
+      </c>
+      <c r="I143">
+        <v>1.3213029999999999</v>
+      </c>
+      <c r="J143">
+        <v>41.952380949999998</v>
+      </c>
+      <c r="K143">
+        <v>160</v>
+      </c>
+      <c r="L143" t="s">
+        <v>30</v>
+      </c>
+      <c r="M143">
+        <v>4405</v>
+      </c>
+      <c r="N143" t="s">
+        <v>63</v>
+      </c>
+      <c r="O143">
+        <v>4137</v>
+      </c>
+      <c r="P143">
+        <v>1064.781242</v>
+      </c>
+      <c r="Q143">
+        <v>105</v>
+      </c>
+      <c r="S143">
+        <v>41.952381000000003</v>
+      </c>
+      <c r="T143">
+        <v>2.538071</v>
+      </c>
+      <c r="U143">
+        <v>118</v>
+      </c>
+      <c r="V143">
+        <v>2.8523079999999998</v>
+      </c>
+      <c r="W143">
+        <v>37.330508000000002</v>
+      </c>
+      <c r="X143">
+        <v>84</v>
+      </c>
+      <c r="Y143">
+        <v>52.440475999999997</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>25</v>
+      </c>
+      <c r="B144" t="s">
+        <v>26</v>
+      </c>
+      <c r="C144" t="s">
+        <v>216</v>
+      </c>
+      <c r="D144" t="s">
+        <v>38</v>
+      </c>
+      <c r="E144" t="s">
+        <v>29</v>
+      </c>
+      <c r="F144">
+        <v>77</v>
+      </c>
+      <c r="G144" t="s">
+        <v>39</v>
+      </c>
+      <c r="H144">
+        <v>2800</v>
+      </c>
+      <c r="I144">
+        <v>1.076071</v>
+      </c>
+      <c r="J144">
+        <v>56.87012987</v>
+      </c>
+      <c r="K144">
+        <v>160</v>
+      </c>
+      <c r="L144" t="s">
+        <v>30</v>
+      </c>
+      <c r="M144">
+        <v>4379</v>
+      </c>
+      <c r="N144" t="s">
+        <v>63</v>
+      </c>
+      <c r="O144">
+        <v>3013</v>
+      </c>
+      <c r="P144">
+        <v>1453.368735</v>
+      </c>
+      <c r="Q144">
+        <v>77</v>
+      </c>
+      <c r="S144">
+        <v>56.870130000000003</v>
+      </c>
+      <c r="T144">
+        <v>2.5555919999999999</v>
+      </c>
+      <c r="U144">
+        <v>74</v>
+      </c>
+      <c r="V144">
+        <v>2.4560240000000002</v>
+      </c>
+      <c r="W144">
+        <v>59.175676000000003</v>
+      </c>
+      <c r="X144">
+        <v>1</v>
+      </c>
+      <c r="Y144">
+        <v>4379</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>25</v>
+      </c>
+      <c r="B145" t="s">
+        <v>26</v>
+      </c>
+      <c r="C145" t="s">
+        <v>217</v>
+      </c>
+      <c r="D145" t="s">
+        <v>38</v>
+      </c>
+      <c r="E145" t="s">
+        <v>29</v>
+      </c>
+      <c r="F145">
+        <v>138</v>
+      </c>
+      <c r="G145" t="s">
+        <v>39</v>
+      </c>
+      <c r="H145">
+        <v>5562</v>
+      </c>
+      <c r="I145">
+        <v>1.3881699999999999</v>
+      </c>
+      <c r="J145">
+        <v>31.942028990000001</v>
+      </c>
+      <c r="K145">
+        <v>160</v>
+      </c>
+      <c r="L145" t="s">
+        <v>30</v>
+      </c>
+      <c r="M145">
+        <v>4408</v>
+      </c>
+      <c r="N145" t="s">
+        <v>63</v>
+      </c>
+      <c r="O145">
+        <v>7721</v>
+      </c>
+      <c r="P145">
+        <v>570.91050399999995</v>
+      </c>
+      <c r="Q145">
+        <v>138</v>
+      </c>
+      <c r="S145">
+        <v>31.942029000000002</v>
+      </c>
+      <c r="T145">
+        <v>1.7873330000000001</v>
+      </c>
+      <c r="U145">
+        <v>187</v>
+      </c>
+      <c r="V145">
+        <v>2.4219659999999998</v>
+      </c>
+      <c r="W145">
+        <v>23.572192999999999</v>
+      </c>
+      <c r="X145">
+        <v>149</v>
+      </c>
+      <c r="Y145">
+        <v>29.583893</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>25</v>
+      </c>
+      <c r="B146" t="s">
+        <v>26</v>
+      </c>
+      <c r="C146" t="s">
+        <v>218</v>
+      </c>
+      <c r="D146" t="s">
+        <v>38</v>
+      </c>
+      <c r="E146" t="s">
+        <v>29</v>
+      </c>
+      <c r="F146">
+        <v>105</v>
+      </c>
+      <c r="G146" t="s">
+        <v>39</v>
+      </c>
+      <c r="H146">
+        <v>3789</v>
+      </c>
+      <c r="I146">
+        <v>1.8287150000000001</v>
+      </c>
+      <c r="J146">
+        <v>41.876190479999998</v>
+      </c>
+      <c r="K146">
+        <v>160</v>
+      </c>
+      <c r="L146" t="s">
+        <v>30</v>
+      </c>
+      <c r="M146">
+        <v>4397</v>
+      </c>
+      <c r="N146" t="s">
+        <v>63</v>
+      </c>
+      <c r="O146">
+        <v>6929</v>
+      </c>
+      <c r="P146">
+        <v>634.57930399999998</v>
+      </c>
+      <c r="Q146">
+        <v>105</v>
+      </c>
+      <c r="S146">
+        <v>41.876190000000001</v>
+      </c>
+      <c r="T146">
+        <v>1.5153700000000001</v>
+      </c>
+      <c r="U146">
+        <v>145</v>
+      </c>
+      <c r="V146">
+        <v>2.092654</v>
+      </c>
+      <c r="W146">
+        <v>30.324138000000001</v>
+      </c>
+      <c r="X146">
+        <v>110</v>
+      </c>
+      <c r="Y146">
+        <v>39.972726999999999</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>25</v>
+      </c>
+      <c r="B147" t="s">
+        <v>26</v>
+      </c>
+      <c r="C147" t="s">
+        <v>219</v>
+      </c>
+      <c r="D147" t="s">
+        <v>38</v>
+      </c>
+      <c r="E147" t="s">
+        <v>29</v>
+      </c>
+      <c r="F147">
+        <v>59</v>
+      </c>
+      <c r="G147" t="s">
+        <v>39</v>
+      </c>
+      <c r="H147">
+        <v>2518</v>
+      </c>
+      <c r="I147">
+        <v>1.292295</v>
+      </c>
+      <c r="J147">
+        <v>74.813559319999996</v>
+      </c>
+      <c r="K147">
+        <v>160</v>
+      </c>
+      <c r="L147" t="s">
+        <v>30</v>
+      </c>
+      <c r="M147">
+        <v>4414</v>
+      </c>
+      <c r="N147" t="s">
+        <v>63</v>
+      </c>
+      <c r="O147">
+        <v>3254</v>
+      </c>
+      <c r="P147">
+        <v>1356.4843269999999</v>
+      </c>
+      <c r="Q147">
+        <v>59</v>
+      </c>
+      <c r="S147">
+        <v>74.813558999999998</v>
+      </c>
+      <c r="T147">
+        <v>1.813153</v>
+      </c>
+      <c r="U147">
+        <v>63</v>
+      </c>
+      <c r="V147">
+        <v>1.9360790000000001</v>
+      </c>
+      <c r="W147">
+        <v>70.063491999999997</v>
+      </c>
+      <c r="X147">
+        <v>48</v>
+      </c>
+      <c r="Y147">
+        <v>91.958332999999996</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>25</v>
+      </c>
+      <c r="B148" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148" t="s">
+        <v>220</v>
+      </c>
+      <c r="D148" t="s">
+        <v>38</v>
+      </c>
+      <c r="E148" t="s">
+        <v>29</v>
+      </c>
+      <c r="F148">
+        <v>155</v>
+      </c>
+      <c r="G148" t="s">
+        <v>39</v>
+      </c>
+      <c r="H148">
+        <v>3345</v>
+      </c>
+      <c r="I148">
+        <v>1.346786</v>
+      </c>
+      <c r="J148">
+        <v>28.458064520000001</v>
+      </c>
+      <c r="K148">
+        <v>160</v>
+      </c>
+      <c r="L148" t="s">
+        <v>30</v>
+      </c>
+      <c r="M148">
+        <v>4411</v>
+      </c>
+      <c r="N148" t="s">
+        <v>63</v>
+      </c>
+      <c r="O148">
+        <v>4505</v>
+      </c>
+      <c r="P148">
+        <v>979.13429499999995</v>
+      </c>
+      <c r="Q148">
+        <v>155</v>
+      </c>
+      <c r="S148">
+        <v>28.458065000000001</v>
+      </c>
+      <c r="T148">
+        <v>3.4406219999999998</v>
+      </c>
+      <c r="U148">
+        <v>163</v>
+      </c>
+      <c r="V148">
+        <v>3.6182020000000001</v>
+      </c>
+      <c r="W148">
+        <v>27.061350000000001</v>
+      </c>
+      <c r="X148">
+        <v>104</v>
+      </c>
+      <c r="Y148">
+        <v>42.413462000000003</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>25</v>
+      </c>
+      <c r="B149" t="s">
+        <v>26</v>
+      </c>
+      <c r="C149" t="s">
+        <v>221</v>
+      </c>
+      <c r="D149" t="s">
+        <v>28</v>
+      </c>
+      <c r="E149" t="s">
+        <v>29</v>
+      </c>
+      <c r="F149">
+        <v>104</v>
+      </c>
+      <c r="G149" t="s">
+        <v>39</v>
+      </c>
+      <c r="H149">
+        <v>4251</v>
+      </c>
+      <c r="I149">
+        <v>1.23665</v>
+      </c>
+      <c r="J149">
+        <v>42.38461538</v>
+      </c>
+      <c r="K149">
+        <v>160</v>
+      </c>
+      <c r="L149" t="s">
+        <v>30</v>
+      </c>
+      <c r="M149">
+        <v>4408</v>
+      </c>
+      <c r="N149" t="s">
+        <v>63</v>
+      </c>
+      <c r="O149">
+        <v>5257</v>
+      </c>
+      <c r="P149">
+        <v>838.50104599999997</v>
+      </c>
+      <c r="Q149">
+        <v>104</v>
+      </c>
+      <c r="S149">
+        <v>42.384614999999997</v>
+      </c>
+      <c r="T149">
+        <v>1.978315</v>
+      </c>
+      <c r="U149">
+        <v>111</v>
+      </c>
+      <c r="V149">
+        <v>2.1114700000000002</v>
+      </c>
+      <c r="W149">
+        <v>39.711711999999999</v>
+      </c>
+      <c r="X149">
+        <v>79</v>
+      </c>
+      <c r="Y149">
+        <v>55.797468000000002</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>25</v>
+      </c>
+      <c r="B150" t="s">
+        <v>26</v>
+      </c>
+      <c r="C150" t="s">
+        <v>222</v>
+      </c>
+      <c r="D150" t="s">
+        <v>87</v>
+      </c>
+      <c r="E150" t="s">
+        <v>29</v>
+      </c>
+      <c r="F150">
+        <v>119</v>
+      </c>
+      <c r="G150" t="s">
+        <v>39</v>
+      </c>
+      <c r="H150">
+        <v>3847</v>
+      </c>
+      <c r="I150">
+        <v>1.981544</v>
+      </c>
+      <c r="J150">
+        <v>74.210084030000004</v>
+      </c>
+      <c r="K150">
+        <v>320</v>
+      </c>
+      <c r="L150" t="s">
+        <v>30</v>
+      </c>
+      <c r="M150">
+        <v>8831</v>
+      </c>
+      <c r="N150" t="s">
+        <v>187</v>
+      </c>
+      <c r="O150">
+        <v>7623</v>
+      </c>
+      <c r="P150">
+        <v>1158.467795</v>
+      </c>
+      <c r="Q150">
+        <v>119</v>
+      </c>
+      <c r="S150">
+        <v>74.210083999999995</v>
+      </c>
+      <c r="T150">
+        <v>1.5610649999999999</v>
+      </c>
+      <c r="U150">
+        <v>128</v>
+      </c>
+      <c r="V150">
+        <v>1.6791290000000001</v>
+      </c>
+      <c r="W150">
+        <v>68.992187999999999</v>
+      </c>
+      <c r="X150">
+        <v>82</v>
+      </c>
+      <c r="Y150">
+        <v>107.695122</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>25</v>
+      </c>
+      <c r="B151" t="s">
+        <v>26</v>
+      </c>
+      <c r="C151" t="s">
+        <v>223</v>
+      </c>
+      <c r="D151" t="s">
+        <v>38</v>
+      </c>
+      <c r="E151" t="s">
+        <v>29</v>
+      </c>
+      <c r="F151">
+        <v>174</v>
+      </c>
+      <c r="G151" t="s">
+        <v>39</v>
+      </c>
+      <c r="H151">
+        <v>4588</v>
+      </c>
+      <c r="I151">
+        <v>1.3221449999999999</v>
+      </c>
+      <c r="J151">
+        <v>25.316091950000001</v>
+      </c>
+      <c r="K151">
+        <v>160</v>
+      </c>
+      <c r="L151" t="s">
+        <v>30</v>
+      </c>
+      <c r="M151">
+        <v>4405</v>
+      </c>
+      <c r="N151" t="s">
+        <v>224</v>
+      </c>
+      <c r="O151">
+        <v>6066</v>
+      </c>
+      <c r="P151">
+        <v>726.17870100000005</v>
+      </c>
+      <c r="Q151">
+        <v>174</v>
+      </c>
+      <c r="S151">
+        <v>25.316092000000001</v>
+      </c>
+      <c r="T151">
+        <v>2.8684470000000002</v>
+      </c>
+      <c r="U151">
+        <v>219</v>
+      </c>
+      <c r="V151">
+        <v>3.610287</v>
+      </c>
+      <c r="W151">
+        <v>20.114155</v>
+      </c>
+      <c r="X151">
+        <v>188</v>
+      </c>
+      <c r="Y151">
+        <v>23.430851000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>25</v>
+      </c>
+      <c r="B152" t="s">
+        <v>26</v>
+      </c>
+      <c r="C152" t="s">
+        <v>225</v>
+      </c>
+      <c r="D152" t="s">
+        <v>38</v>
+      </c>
+      <c r="E152" t="s">
+        <v>29</v>
+      </c>
+      <c r="F152">
+        <v>177</v>
+      </c>
+      <c r="G152" t="s">
+        <v>39</v>
+      </c>
+      <c r="H152">
+        <v>3572</v>
+      </c>
+      <c r="I152">
+        <v>1.649216</v>
+      </c>
+      <c r="J152">
+        <v>24.960451979999998</v>
+      </c>
+      <c r="K152">
+        <v>160</v>
+      </c>
+      <c r="L152" t="s">
+        <v>30</v>
+      </c>
+      <c r="M152">
+        <v>4418</v>
+      </c>
+      <c r="N152" t="s">
+        <v>224</v>
+      </c>
+      <c r="O152">
+        <v>5891</v>
+      </c>
+      <c r="P152">
+        <v>749.95756200000005</v>
+      </c>
+      <c r="Q152">
+        <v>177</v>
+      </c>
+      <c r="S152">
+        <v>24.960452</v>
+      </c>
+      <c r="T152">
+        <v>3.0045829999999998</v>
+      </c>
+      <c r="U152">
+        <v>201</v>
+      </c>
+      <c r="V152">
+        <v>3.4119839999999999</v>
+      </c>
+      <c r="W152">
+        <v>21.9801</v>
+      </c>
+      <c r="X152">
+        <v>4</v>
+      </c>
+      <c r="Y152">
+        <v>1104.5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>25</v>
+      </c>
+      <c r="B153" t="s">
+        <v>26</v>
+      </c>
+      <c r="C153" t="s">
+        <v>226</v>
+      </c>
+      <c r="D153" t="s">
+        <v>38</v>
+      </c>
+      <c r="E153" t="s">
+        <v>29</v>
+      </c>
+      <c r="F153">
+        <v>156</v>
+      </c>
+      <c r="G153" t="s">
+        <v>39</v>
+      </c>
+      <c r="H153">
+        <v>2925</v>
+      </c>
+      <c r="I153">
+        <v>1.4618800000000001</v>
+      </c>
+      <c r="J153">
+        <v>28.121794869999999</v>
+      </c>
+      <c r="K153">
+        <v>160</v>
+      </c>
+      <c r="L153" t="s">
+        <v>30</v>
+      </c>
+      <c r="M153">
+        <v>4387</v>
+      </c>
+      <c r="N153" t="s">
+        <v>224</v>
+      </c>
+      <c r="O153">
+        <v>4276</v>
+      </c>
+      <c r="P153">
+        <v>1025.95884</v>
+      </c>
+      <c r="Q153">
+        <v>156</v>
+      </c>
+      <c r="S153">
+        <v>28.121794999999999</v>
+      </c>
+      <c r="T153">
+        <v>3.648269</v>
+      </c>
+      <c r="U153">
+        <v>199</v>
+      </c>
+      <c r="V153">
+        <v>4.6538820000000003</v>
+      </c>
+      <c r="W153">
+        <v>22.045226</v>
+      </c>
+      <c r="X153">
+        <v>155</v>
+      </c>
+      <c r="Y153">
+        <v>28.303225999999999</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>25</v>
+      </c>
+      <c r="B154" t="s">
+        <v>26</v>
+      </c>
+      <c r="C154" t="s">
+        <v>227</v>
+      </c>
+      <c r="D154" t="s">
+        <v>38</v>
+      </c>
+      <c r="E154" t="s">
+        <v>29</v>
+      </c>
+      <c r="F154">
+        <v>254</v>
+      </c>
+      <c r="G154" t="s">
+        <v>39</v>
+      </c>
+      <c r="H154">
+        <v>5361</v>
+      </c>
+      <c r="I154">
+        <v>1.3159860000000001</v>
+      </c>
+      <c r="J154">
+        <v>17.377952759999999</v>
+      </c>
+      <c r="K154">
+        <v>160</v>
+      </c>
+      <c r="L154" t="s">
+        <v>30</v>
+      </c>
+      <c r="M154">
+        <v>4414</v>
+      </c>
+      <c r="N154" t="s">
+        <v>224</v>
+      </c>
+      <c r="O154">
+        <v>7055</v>
+      </c>
+      <c r="P154">
+        <v>625.65556300000003</v>
+      </c>
+      <c r="Q154">
+        <v>254</v>
+      </c>
+      <c r="S154">
+        <v>17.377953000000002</v>
+      </c>
+      <c r="T154">
+        <v>3.6002830000000001</v>
+      </c>
+      <c r="U154">
+        <v>275</v>
+      </c>
+      <c r="V154">
+        <v>3.897945</v>
+      </c>
+      <c r="W154">
+        <v>16.050909000000001</v>
+      </c>
+      <c r="X154">
+        <v>228</v>
+      </c>
+      <c r="Y154">
+        <v>19.359649000000001</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>25</v>
+      </c>
+      <c r="B155" t="s">
+        <v>26</v>
+      </c>
+      <c r="C155" t="s">
+        <v>228</v>
+      </c>
+      <c r="D155" t="s">
+        <v>38</v>
+      </c>
+      <c r="E155" t="s">
+        <v>29</v>
+      </c>
+      <c r="F155">
+        <v>75</v>
+      </c>
+      <c r="G155" t="s">
+        <v>39</v>
+      </c>
+      <c r="H155">
+        <v>2552</v>
+      </c>
+      <c r="I155">
+        <v>1.2268810000000001</v>
+      </c>
+      <c r="J155">
+        <v>58.68</v>
+      </c>
+      <c r="K155">
+        <v>160</v>
+      </c>
+      <c r="L155" t="s">
+        <v>30</v>
+      </c>
+      <c r="M155">
+        <v>4401</v>
+      </c>
+      <c r="N155" t="s">
+        <v>224</v>
+      </c>
+      <c r="O155">
+        <v>3131</v>
+      </c>
+      <c r="P155">
+        <v>1405.6212069999999</v>
+      </c>
+      <c r="Q155">
+        <v>75</v>
+      </c>
+      <c r="S155">
+        <v>58.68</v>
+      </c>
+      <c r="T155">
+        <v>2.3954010000000001</v>
+      </c>
+      <c r="U155">
+        <v>79</v>
+      </c>
+      <c r="V155">
+        <v>2.5231560000000002</v>
+      </c>
+      <c r="W155">
+        <v>55.708860999999999</v>
+      </c>
+      <c r="X155">
+        <v>39</v>
+      </c>
+      <c r="Y155">
+        <v>112.846154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>25</v>
+      </c>
+      <c r="B156" t="s">
+        <v>26</v>
+      </c>
+      <c r="C156" t="s">
+        <v>229</v>
+      </c>
+      <c r="D156" t="s">
+        <v>38</v>
+      </c>
+      <c r="E156" t="s">
+        <v>29</v>
+      </c>
+      <c r="F156">
+        <v>419</v>
+      </c>
+      <c r="G156" t="s">
+        <v>39</v>
+      </c>
+      <c r="H156">
+        <v>5517</v>
+      </c>
+      <c r="I156">
+        <v>1.3179259999999999</v>
+      </c>
+      <c r="J156">
+        <v>10.53699284</v>
+      </c>
+      <c r="K156">
+        <v>160</v>
+      </c>
+      <c r="L156" t="s">
+        <v>30</v>
+      </c>
+      <c r="M156">
+        <v>4415</v>
+      </c>
+      <c r="N156" t="s">
+        <v>224</v>
+      </c>
+      <c r="O156">
+        <v>7271</v>
+      </c>
+      <c r="P156">
+        <v>607.20671200000004</v>
+      </c>
+      <c r="Q156">
+        <v>419</v>
+      </c>
+      <c r="S156">
+        <v>10.536993000000001</v>
+      </c>
+      <c r="T156">
+        <v>5.7626189999999999</v>
+      </c>
+      <c r="U156">
+        <v>491</v>
+      </c>
+      <c r="V156">
+        <v>6.7528540000000001</v>
+      </c>
+      <c r="W156">
+        <v>8.9918530000000008</v>
+      </c>
+      <c r="X156">
+        <v>1</v>
+      </c>
+      <c r="Y156">
+        <v>4415</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>25</v>
+      </c>
+      <c r="B157" t="s">
+        <v>26</v>
+      </c>
+      <c r="C157" t="s">
+        <v>230</v>
+      </c>
+      <c r="D157" t="s">
+        <v>38</v>
+      </c>
+      <c r="E157" t="s">
+        <v>29</v>
+      </c>
+      <c r="F157">
+        <v>318</v>
+      </c>
+      <c r="G157" t="s">
+        <v>39</v>
+      </c>
+      <c r="H157">
+        <v>3975</v>
+      </c>
+      <c r="I157">
+        <v>1.303396</v>
+      </c>
+      <c r="J157">
+        <v>13.808176100000001</v>
+      </c>
+      <c r="K157">
+        <v>160</v>
+      </c>
+      <c r="L157" t="s">
+        <v>30</v>
+      </c>
+      <c r="M157">
+        <v>4391</v>
+      </c>
+      <c r="N157" t="s">
+        <v>224</v>
+      </c>
+      <c r="O157">
+        <v>5181</v>
+      </c>
+      <c r="P157">
+        <v>847.51978399999996</v>
+      </c>
+      <c r="Q157">
+        <v>318</v>
+      </c>
+      <c r="S157">
+        <v>13.808176</v>
+      </c>
+      <c r="T157">
+        <v>6.1378110000000001</v>
+      </c>
+      <c r="U157">
+        <v>403</v>
+      </c>
+      <c r="V157">
+        <v>7.7784209999999998</v>
+      </c>
+      <c r="W157">
+        <v>10.895782000000001</v>
+      </c>
+      <c r="X157">
+        <v>315</v>
+      </c>
+      <c r="Y157">
+        <v>13.939683</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>25</v>
+      </c>
+      <c r="B158" t="s">
+        <v>26</v>
+      </c>
+      <c r="C158" t="s">
+        <v>231</v>
+      </c>
+      <c r="D158" t="s">
+        <v>38</v>
+      </c>
+      <c r="E158" t="s">
+        <v>29</v>
+      </c>
+      <c r="F158">
+        <v>64</v>
+      </c>
+      <c r="G158" t="s">
+        <v>39</v>
+      </c>
+      <c r="H158">
+        <v>2044</v>
+      </c>
+      <c r="I158">
+        <v>1.127691</v>
+      </c>
+      <c r="J158">
+        <v>62.609375</v>
+      </c>
+      <c r="K158">
+        <v>160</v>
+      </c>
+      <c r="L158" t="s">
+        <v>30</v>
+      </c>
+      <c r="M158">
+        <v>4007</v>
+      </c>
+      <c r="N158" t="s">
+        <v>232</v>
+      </c>
+      <c r="O158">
+        <v>2305</v>
+      </c>
+      <c r="P158">
+        <v>1738.394794</v>
+      </c>
+      <c r="Q158">
+        <v>64</v>
+      </c>
+      <c r="S158">
+        <v>62.609375</v>
+      </c>
+      <c r="T158">
+        <v>2.776573</v>
+      </c>
+      <c r="U158">
+        <v>65</v>
+      </c>
+      <c r="V158">
+        <v>2.819957</v>
+      </c>
+      <c r="W158">
+        <v>61.646154000000003</v>
+      </c>
+      <c r="X158">
+        <v>45</v>
+      </c>
+      <c r="Y158">
+        <v>89.044443999999999</v>
+      </c>
+    </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>25</v>
+      </c>
+      <c r="B159" t="s">
+        <v>26</v>
+      </c>
+      <c r="C159" t="s">
+        <v>233</v>
+      </c>
+      <c r="D159" t="s">
+        <v>38</v>
+      </c>
+      <c r="E159" t="s">
+        <v>29</v>
+      </c>
+      <c r="F159">
+        <v>107</v>
+      </c>
+      <c r="G159" t="s">
+        <v>39</v>
+      </c>
+      <c r="H159">
+        <v>2612</v>
+      </c>
+      <c r="I159">
+        <v>1.6343799999999999</v>
+      </c>
+      <c r="J159">
+        <v>37.168224299999999</v>
+      </c>
+      <c r="K159">
+        <v>160</v>
+      </c>
+      <c r="L159" t="s">
+        <v>30</v>
+      </c>
+      <c r="M159">
+        <v>3977</v>
+      </c>
+      <c r="N159" t="s">
+        <v>232</v>
+      </c>
+      <c r="O159">
+        <v>4269</v>
+      </c>
+      <c r="P159">
+        <v>931.59990600000003</v>
+      </c>
+      <c r="Q159">
+        <v>107</v>
+      </c>
+      <c r="S159">
+        <v>37.168224000000002</v>
+      </c>
+      <c r="T159">
+        <v>2.5064419999999998</v>
+      </c>
+      <c r="U159">
+        <v>141</v>
+      </c>
+      <c r="V159">
+        <v>3.3028810000000002</v>
+      </c>
+      <c r="W159">
+        <v>28.205673999999998</v>
+      </c>
+      <c r="X159">
+        <v>112</v>
+      </c>
+      <c r="Y159">
+        <v>35.508929000000002</v>
+      </c>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>25</v>
+      </c>
+      <c r="B160" t="s">
+        <v>26</v>
+      </c>
+      <c r="C160" t="s">
+        <v>234</v>
+      </c>
+      <c r="D160" t="s">
+        <v>38</v>
+      </c>
+      <c r="E160" t="s">
+        <v>29</v>
+      </c>
+      <c r="F160">
+        <v>107</v>
+      </c>
+      <c r="G160" t="s">
+        <v>39</v>
+      </c>
+      <c r="H160">
+        <v>2800</v>
+      </c>
+      <c r="I160">
+        <v>1.7607139999999999</v>
+      </c>
+      <c r="J160">
+        <v>37.336448599999997</v>
+      </c>
+      <c r="K160">
+        <v>160</v>
+      </c>
+      <c r="L160" t="s">
+        <v>30</v>
+      </c>
+      <c r="M160">
+        <v>3995</v>
+      </c>
+      <c r="N160" t="s">
+        <v>232</v>
+      </c>
+      <c r="O160">
+        <v>4930</v>
+      </c>
+      <c r="P160">
+        <v>810.34482800000001</v>
+      </c>
+      <c r="Q160">
+        <v>107</v>
+      </c>
+      <c r="S160">
+        <v>37.336449000000002</v>
+      </c>
+      <c r="T160">
+        <v>2.170385</v>
+      </c>
+      <c r="U160">
+        <v>133</v>
+      </c>
+      <c r="V160">
+        <v>2.6977690000000001</v>
+      </c>
+      <c r="W160">
+        <v>30.037593999999999</v>
+      </c>
+      <c r="X160">
+        <v>1</v>
+      </c>
+      <c r="Y160">
+        <v>3995</v>
+      </c>
+    </row>
+    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>25</v>
+      </c>
+      <c r="B161" t="s">
+        <v>26</v>
+      </c>
+      <c r="C161" t="s">
+        <v>235</v>
+      </c>
+      <c r="D161" t="s">
+        <v>38</v>
+      </c>
+      <c r="E161" t="s">
+        <v>29</v>
+      </c>
+      <c r="F161">
+        <v>117</v>
+      </c>
+      <c r="G161" t="s">
+        <v>39</v>
+      </c>
+      <c r="H161">
+        <v>3230</v>
+      </c>
+      <c r="I161">
+        <v>1.3743030000000001</v>
+      </c>
+      <c r="J161">
+        <v>34.14529915</v>
+      </c>
+      <c r="K161">
+        <v>160</v>
+      </c>
+      <c r="L161" t="s">
+        <v>30</v>
+      </c>
+      <c r="M161">
+        <v>3995</v>
+      </c>
+      <c r="N161" t="s">
+        <v>232</v>
+      </c>
+      <c r="O161">
+        <v>4439</v>
+      </c>
+      <c r="P161">
+        <v>899.97747200000003</v>
+      </c>
+      <c r="Q161">
+        <v>117</v>
+      </c>
+      <c r="S161">
+        <v>34.145299000000001</v>
+      </c>
+      <c r="T161">
+        <v>2.635729</v>
+      </c>
+      <c r="U161">
+        <v>144</v>
+      </c>
+      <c r="V161">
+        <v>3.2439740000000001</v>
+      </c>
+      <c r="W161">
+        <v>27.743055999999999</v>
+      </c>
+      <c r="X161">
+        <v>115</v>
+      </c>
+      <c r="Y161">
+        <v>34.739130000000003</v>
+      </c>
+    </row>
+    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>25</v>
+      </c>
+      <c r="B162" t="s">
+        <v>26</v>
+      </c>
+      <c r="C162" t="s">
+        <v>172</v>
+      </c>
+      <c r="D162" t="s">
+        <v>38</v>
+      </c>
+      <c r="E162" t="s">
+        <v>29</v>
+      </c>
+      <c r="F162">
+        <v>145</v>
+      </c>
+      <c r="G162" t="s">
+        <v>39</v>
+      </c>
+      <c r="H162">
+        <v>2573</v>
+      </c>
+      <c r="I162">
+        <v>1.251069</v>
+      </c>
+      <c r="J162">
+        <v>20.855172410000002</v>
+      </c>
+      <c r="K162">
+        <v>160</v>
+      </c>
+      <c r="L162" t="s">
+        <v>30</v>
+      </c>
+      <c r="M162">
+        <v>3024</v>
+      </c>
+      <c r="N162" t="s">
+        <v>77</v>
+      </c>
+      <c r="O162">
+        <v>3219</v>
+      </c>
+      <c r="P162">
+        <v>939.42218100000002</v>
+      </c>
+      <c r="Q162">
+        <v>145</v>
+      </c>
+      <c r="S162">
+        <v>20.855172</v>
+      </c>
+      <c r="T162">
+        <v>4.504505</v>
+      </c>
+      <c r="U162">
+        <v>151</v>
+      </c>
+      <c r="V162">
+        <v>4.6908979999999998</v>
+      </c>
+      <c r="W162">
+        <v>20.026489999999999</v>
+      </c>
+      <c r="X162">
+        <v>3</v>
+      </c>
+      <c r="Y162">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>25</v>
+      </c>
+      <c r="B163" t="s">
+        <v>26</v>
+      </c>
+      <c r="C163" t="s">
+        <v>236</v>
+      </c>
+      <c r="D163" t="s">
+        <v>28</v>
+      </c>
+      <c r="E163" t="s">
+        <v>29</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>160</v>
+      </c>
+      <c r="L163" t="s">
+        <v>30</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+      <c r="N163" t="s">
+        <v>237</v>
+      </c>
+      <c r="O163">
+        <v>0</v>
+      </c>
+      <c r="P163">
+        <v>0</v>
+      </c>
+      <c r="U163">
+        <v>0</v>
+      </c>
+      <c r="V163">
+        <v>0</v>
+      </c>
+      <c r="W163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>25</v>
+      </c>
+      <c r="B164" t="s">
+        <v>26</v>
+      </c>
+      <c r="C164" t="s">
+        <v>238</v>
+      </c>
+      <c r="D164" t="s">
+        <v>28</v>
+      </c>
+      <c r="E164" t="s">
+        <v>29</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>160</v>
+      </c>
+      <c r="L164" t="s">
+        <v>30</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="N164" t="s">
+        <v>148</v>
+      </c>
+      <c r="O164">
+        <v>0</v>
+      </c>
+      <c r="P164">
+        <v>0</v>
+      </c>
+      <c r="U164">
+        <v>0</v>
+      </c>
+      <c r="V164">
+        <v>0</v>
+      </c>
+      <c r="W164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>25</v>
+      </c>
+      <c r="B165" t="s">
+        <v>26</v>
+      </c>
+      <c r="C165" t="s">
+        <v>239</v>
+      </c>
+      <c r="D165" t="s">
+        <v>28</v>
+      </c>
+      <c r="E165" t="s">
+        <v>29</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>160</v>
+      </c>
+      <c r="L165" t="s">
+        <v>30</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+      <c r="N165" t="s">
+        <v>148</v>
+      </c>
+      <c r="O165">
+        <v>0</v>
+      </c>
+      <c r="P165">
+        <v>0</v>
+      </c>
+      <c r="U165">
+        <v>0</v>
+      </c>
+      <c r="V165">
+        <v>0</v>
+      </c>
+      <c r="W165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>25</v>
+      </c>
+      <c r="B166" t="s">
+        <v>26</v>
+      </c>
+      <c r="C166" t="s">
+        <v>240</v>
+      </c>
+      <c r="D166" t="s">
+        <v>28</v>
+      </c>
+      <c r="E166" t="s">
+        <v>29</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>320</v>
+      </c>
+      <c r="L166" t="s">
+        <v>30</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="N166" t="s">
+        <v>148</v>
+      </c>
+      <c r="O166">
+        <v>0</v>
+      </c>
+      <c r="P166">
+        <v>0</v>
+      </c>
+      <c r="U166">
+        <v>0</v>
+      </c>
+      <c r="V166">
+        <v>0</v>
+      </c>
+      <c r="W166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>25</v>
+      </c>
+      <c r="B167" t="s">
+        <v>26</v>
+      </c>
+      <c r="C167" t="s">
+        <v>241</v>
+      </c>
+      <c r="D167" t="s">
+        <v>28</v>
+      </c>
+      <c r="E167" t="s">
+        <v>29</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>160</v>
+      </c>
+      <c r="L167" t="s">
+        <v>30</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+      <c r="N167" t="s">
+        <v>148</v>
+      </c>
+      <c r="O167">
+        <v>0</v>
+      </c>
+      <c r="P167">
+        <v>0</v>
+      </c>
+      <c r="U167">
+        <v>0</v>
+      </c>
+      <c r="V167">
+        <v>0</v>
+      </c>
+      <c r="W167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>25</v>
+      </c>
+      <c r="B168" t="s">
+        <v>26</v>
+      </c>
+      <c r="C168" t="s">
+        <v>242</v>
+      </c>
+      <c r="D168" t="s">
+        <v>28</v>
+      </c>
+      <c r="E168" t="s">
+        <v>29</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>160</v>
+      </c>
+      <c r="L168" t="s">
+        <v>30</v>
+      </c>
+      <c r="M168">
+        <v>0</v>
+      </c>
+      <c r="N168" t="s">
+        <v>148</v>
+      </c>
+      <c r="O168">
+        <v>0</v>
+      </c>
+      <c r="P168">
+        <v>0</v>
+      </c>
+      <c r="U168">
+        <v>0</v>
+      </c>
+      <c r="V168">
+        <v>0</v>
+      </c>
+      <c r="W168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>25</v>
+      </c>
+      <c r="B169" t="s">
+        <v>26</v>
+      </c>
+      <c r="C169" t="s">
+        <v>243</v>
+      </c>
+      <c r="D169" t="s">
+        <v>28</v>
+      </c>
+      <c r="E169" t="s">
+        <v>29</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>160</v>
+      </c>
+      <c r="L169" t="s">
+        <v>30</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="N169" t="s">
+        <v>103</v>
+      </c>
+      <c r="O169">
+        <v>0</v>
+      </c>
+      <c r="P169">
+        <v>0</v>
+      </c>
+      <c r="U169">
+        <v>0</v>
+      </c>
+      <c r="V169">
+        <v>0</v>
+      </c>
+      <c r="W169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>25</v>
+      </c>
+      <c r="B170" t="s">
+        <v>26</v>
+      </c>
+      <c r="C170" t="s">
+        <v>244</v>
+      </c>
+      <c r="D170" t="s">
+        <v>28</v>
+      </c>
+      <c r="E170" t="s">
+        <v>29</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>160</v>
+      </c>
+      <c r="L170" t="s">
+        <v>30</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170" t="s">
+        <v>103</v>
+      </c>
+      <c r="O170">
+        <v>0</v>
+      </c>
+      <c r="P170">
+        <v>0</v>
+      </c>
+      <c r="U170">
+        <v>0</v>
+      </c>
+      <c r="V170">
+        <v>0</v>
+      </c>
+      <c r="W170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:25" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>25</v>
+      </c>
+      <c r="B171" t="s">
+        <v>26</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D171" t="s">
+        <v>28</v>
+      </c>
+      <c r="E171" t="s">
+        <v>29</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>58000</v>
+      </c>
+      <c r="L171" t="s">
+        <v>30</v>
+      </c>
+      <c r="M171">
+        <v>0</v>
+      </c>
+      <c r="N171" t="s">
+        <v>245</v>
+      </c>
+      <c r="O171">
+        <v>0</v>
+      </c>
+      <c r="P171">
+        <v>0</v>
+      </c>
+      <c r="U171">
+        <v>0</v>
+      </c>
+      <c r="V171">
+        <v>0</v>
+      </c>
+      <c r="W171">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
